--- a/evaluation_layer/eval_methods/Solution wizard evaluation/use cases/UC03_document_rag_evaluation/results/UC03_comparison.xlsx
+++ b/evaluation_layer/eval_methods/Solution wizard evaluation/use cases/UC03_document_rag_evaluation/results/UC03_comparison.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB5D3B7F-A10F-4F1B-A1C2-C2AB8A4C92B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80815661-D3FE-45A6-87E5-3BB1099B675F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -22,25 +22,12 @@
     <sheet name="EQ4 Execution" sheetId="7" r:id="rId7"/>
     <sheet name="PoC Recovery" sheetId="8" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1059" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="583">
   <si>
     <t>UC03 document-RAG evaluation</t>
   </si>
@@ -315,21 +302,15 @@
     <t>initial_prompt.txt; scripted_answers.json</t>
   </si>
   <si>
-    <t>intended_users: employee, manager, knowledge_owner</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT business_spec.intended_users = ["employee", "manager", "knowledge_owner"]; use_case.description = "Role-aware question-answering assistant that retrieves cited answers from internal manufacturing policies, equipment manuals, and management documents..."</t>
+    <t>Employees and managers</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_spec.intended_users = ["employee", "manager"]; conversation L0078: "Employees are the main users."</t>
   </si>
   <si>
     <t>needs_review</t>
   </si>
   <si>
-    <t>employee, manager</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT business_spec.intended_users = ["employee", "manager"]; use_case.description = "Role-aware RAG assistant that answers employee questions over internal manufacturing policies, equipment manuals, and management documents..."</t>
-  </si>
-  <si>
     <t>EQ1-R02</t>
   </si>
   <si>
@@ -339,15 +320,12 @@
     <t>Employees manually search policies, manuals, and management documents.</t>
   </si>
   <si>
-    <t>Employees manually search internal policies, equipment manuals, and management documents</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT business_spec.current_process = "Employees manually search internal policies, equipment manuals, and management documents to find answers; the process is slow and may result in incomplete or unsupported responses."</t>
-  </si>
-  <si>
     <t>Employees manually search across internal policies, equipment manuals, and management documents</t>
   </si>
   <si>
+    <t>GENERATED BLUEPRINT business_spec.current_process = "Employees manually search across internal policies, equipment manuals, and management documents to find answers to their questions, with no systematic way to verify which source supports an answer."</t>
+  </si>
+  <si>
     <t>GENERATED BLUEPRINT business_spec.current_process = "Employees manually search across internal policies, equipment manuals, and management documents to find relevant information, which is slow and can lead to incomplete or unsupported answers."</t>
   </si>
   <si>
@@ -360,13 +338,13 @@
     <t>Manual search is slow and may produce incomplete or unsupported answers.</t>
   </si>
   <si>
-    <t>Manual document search is time-consuming; employees may miss relevant sources; answers are not traceable; process may produce incomplete or unsupported responses</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT business_spec.pain_points[0] = "Manual document search is time-consuming"; business_spec.pain_points[1] = "Employees may miss the most relevant or applicable source"; business_spec.pain_points[3] = "Answers are not traceable to a verified source"; business_spec.current_process = "...the process is slow and may result in incomplete or unsupported responses."</t>
-  </si>
-  <si>
-    <t>Manual search is slow; incomplete or unsupported answers; no access-boundary enforcement</t>
+    <t>Manual search is slow; answers can be incomplete or unsupported because employees may overlook the applicable source</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_spec.pain_points[0] = "Manual search across the document collection is slow"; business_spec.pain_points[1] = "Answers can be incomplete or unsupported because employees may overlook the applicable source"</t>
+  </si>
+  <si>
+    <t>Search is slow; employees may overlook sources; risk of incomplete or unsupported answers</t>
   </si>
   <si>
     <t>GENERATED BLUEPRINT business_spec.pain_points = ["Manual document search is slow and time-consuming", "Employees may overlook the applicable source document", "Risk of incomplete or unsupported answers", "No enforcement of document access boundaries between roles"]</t>
@@ -384,16 +362,16 @@
     <t>scripted_answers.json</t>
   </si>
   <si>
-    <t>knowledge_owners, managers, IT stakeholders; intended users include employee, manager, knowledge_owner; reviewers empty</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT business_spec.stakeholders = ["knowledge_owners", "managers", "IT"]; business_spec.intended_users = ["employee", "manager", "knowledge_owner"]; business_spec.reviewers = []</t>
-  </si>
-  <si>
-    <t>stakeholders: employees, managers, knowledge_owners; reviewers: []</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT business_spec.stakeholders = ["employees", "managers", "knowledge_owners"]; business_spec.reviewers = []; business_process.participants = [{"id":"employee"...}, {"id":"manager"...}, {"id":"gaik_ai_system"...}]</t>
+    <t>Stakeholders: knowledge owners maintain/classify source documents; managers access management-confidential material; employees are primary users; reviewers: []</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_spec.stakeholders = ["knowledge owners (maintain and classify the source documents)", "managers (authorized to access management-confidential material)", "employees (primary users of the assistant)"]; business_spec.reviewers = []; conversation L0080: "reviewers and key stakeholders: Not specified for this evaluation."</t>
+  </si>
+  <si>
+    <t>Stakeholders: employees, managers, knowledge_owners; reviewers: []</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_spec.stakeholders = ["employees", "managers", "knowledge_owners"]; business_spec.reviewers = []</t>
   </si>
   <si>
     <t>EQ1-R05</t>
@@ -405,16 +383,16 @@
     <t>Faster access to reliable internal knowledge with citations and enforced access boundaries.</t>
   </si>
   <si>
-    <t>Employees find reliable answers faster; every factual answer traceable via citations; restricted documents never disclosed to unauthorized roles; reduced risk of incomplete or unsupported answers</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT business_spec.expected_value = ["Employees find reliable answers faster", "Every factual answer is traceable to a verified source via citations", "Restricted documents are never disclosed to unauthorized roles", "Reduced risk of incomplete or unsupported answers"]</t>
-  </si>
-  <si>
-    <t>Faster reliable knowledge access, citations, enforced access boundaries</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT business_spec.expected_value = ["Faster access to reliable internal knowledge", "Traceable answers via source citations", "Enforced access boundaries with no content leakage across roles"]; business_spec.success_criteria = ["Employees find reliable answers faster than manual search", "Answers are verifiable through document citations", "Employees never receive content outside their authorized role", "System correctly refuses to answer from unauthorized content"]</t>
+    <t>Faster access to reliable internal knowledge, traceable answers via citations, enforced access boundaries</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_spec.expected_value = ["faster access to reliable internal knowledge", "traceable answers via citations", "enforced access boundaries that prevent unauthorized disclosure"]</t>
+  </si>
+  <si>
+    <t>Faster access to reliable internal knowledge; traceable answers via citations; enforced access boundaries with no content leakage across roles</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_spec.expected_value = ["Faster access to reliable internal knowledge", "Traceable answers via source citations", "Enforced access boundaries with no content leakage across roles"]</t>
   </si>
   <si>
     <t>EQ1-R06</t>
@@ -429,10 +407,16 @@
     <t>scripted_answers.json; fixtures/rag_test_bundle.json</t>
   </si>
   <si>
+    <t>Three sample PDFs: employee_travel_policy.pdf, mx200_maintenance_manual.pdf, project_aurora_pricing_strategy.pdf</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_spec.poc_goal = "Demonstrate role-aware, citation-grounded question answering over three sample PDFs (employee travel policy, MX-200 maintenance manual, Project Aurora pricing strategy) ..."; technical_spec.data_sources = "PoC uses a local fixture bundle: three sample PDFs (employee_travel_policy.pdf, mx200_maintenance_manual.pdf, project_aurora_pricing_strategy.pdf) plus access_manifest.json and query_set.json, all resolved relative to poc_input_bundle.json."</t>
+  </si>
+  <si>
     <t>employee_travel_policy.pdf, mx200_maintenance_manual.pdf, project_aurora_pricing_strategy.pdf</t>
   </si>
   <si>
-    <t>GENERATED BLUEPRINT business_spec.input_artifacts = ["employee_travel_policy.pdf", "mx200_maintenance_manual.pdf", "project_aurora_pricing_strategy.pdf", "access_manifest.json", "query_set.json", "poc_input_bundle.json"]</t>
+    <t>GENERATED BLUEPRINT business_spec.input_artifacts = ["employee_travel_policy.pdf", "mx200_maintenance_manual.pdf", "project_aurora_pricing_strategy.pdf", "access_manifest.json", "query_set.json", "poc_input_bundle.json"]; conversation L0156 names the three supplied English PDFs.</t>
   </si>
   <si>
     <t>EQ1-R07</t>
@@ -444,16 +428,16 @@
     <t>Text-based PDF documents in English.</t>
   </si>
   <si>
-    <t>PDF (text-based) and language en</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.input_formats[0] = "PDF (text-based, 1-based page numbers)"; technical_spec.language = "en"; technical_spec.input_types = ["pdf", "json"]</t>
-  </si>
-  <si>
-    <t>pdf; language en</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.input_types = ["pdf", "document_collection", "text"]; technical_spec.input_formats = ["pdf", "json"]; technical_spec.language = "en"</t>
+    <t>pdf (text-based, English); language en</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.input_formats[0] = "pdf (text-based, English)"; technical_spec.language = "en"</t>
+  </si>
+  <si>
+    <t>PDF and English (en)</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.input_formats = ["pdf", "json"]; technical_spec.language = "en"; conversation L0156: "three synthetic, text-based English PDFs"</t>
   </si>
   <si>
     <t>EQ1-R08</t>
@@ -468,16 +452,16 @@
     <t>scripted_answers.json; fixtures/poc_input/access_manifest.json</t>
   </si>
   <si>
-    <t>metadata_fields: file_name, page_number, classification, allowed_roles</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT workflow.steps[1].parameters.metadata_fields = ["file_name", "page_number", "classification", "allowed_roles"]; FILE generated_package\poc\run_poc.py build_index docstring = "Each chunk dict: text, file_name, page_number, classification, allowed_roles, embedding"</t>
-  </si>
-  <si>
-    <t>classification, allowed_roles, file_name, page_number metadata preserved</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT workflow.steps[1].parameters.rbac_metadata_fields = ["classification", "allowed_roles", "file_name", "page_number"]; technical_spec.security_constraints = "Role-based access control enforced via per-chunk allowed_roles metadata stored in the vector index."</t>
+    <t>Per-document classification and allowed_roles preserved; citations use [file_name, page_number] with 1-based page numbers; role_&lt;role&gt; metadata flags attached to chunks</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.data_sources = "... plus access_manifest.json ..."; technical_spec.security_constraints = "Role-based access filtering must occur before retrieval..."; workflow.steps[3].parameters.access_control = "Pre-retrieval RBAC: each indexed chunk is tagged with boolean role_&lt;role&gt; metadata flags derived from access_manifest.json's allowed_roles..."; target_output_spec.field_types.citations = "list of [file_name: str, page_number: int (1-based)]"</t>
+  </si>
+  <si>
+    <t>Metadata fields classification, allowed_roles, file_name, page_number preserved for RBAC/citations</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT workflow.steps[1].parameters.rbac_metadata_fields = ["classification", "allowed_roles", "file_name", "page_number"]; conversation L0156: "Each document has a title, filename, classification, allowed-role metadata, and 1-based PDF page-number metadata."</t>
   </si>
   <si>
     <t>EQ1-R09</t>
@@ -492,10 +476,7 @@
     <t>RAGAnswerRecord</t>
   </si>
   <si>
-    <t>GENERATED BLUEPRINT target_output_spec.schema_name = "RAGAnswerRecord"; business_spec.target_outputs[0] = "RAGAnswerRecord JSON list (query_id, role, question, access_decision, answer, citations, refusal_reason)"</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.schema_name = "RAGAnswerRecord"; business_spec.target_outputs = ["rag_answer_records_json"]</t>
+    <t>GENERATED BLUEPRINT target_output_spec.schema_name = "RAGAnswerRecord"</t>
   </si>
   <si>
     <t>EQ1-R10</t>
@@ -507,16 +488,16 @@
     <t>query_id; string; required and preserved from the input query.</t>
   </si>
   <si>
-    <t>query_id: str; required; unique query identifier from query_set.json</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.fields[0] = "query_id"; target_output_spec.field_types.query_id = "str"; target_output_spec.required_fields includes "query_id"; target_output_spec.field_descriptions.query_id = "Unique query identifier from query_set.json"</t>
-  </si>
-  <si>
-    <t>query_id required; unique identifier e.g. Q01</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.fields = ["query_id", "role", "question", "access_decision", "answer", "citations", "refusal_reason"]; target_output_spec.required_fields = ["query_id", "role", "question", "access_decision", "answer", "citations"]; target_output_spec.field_descriptions.query_id = "Unique identifier for the query, e.g. Q01"</t>
+    <t>query_id: str; preserved unchanged from input</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.field_types.query_id = "str"; target_output_spec.field_descriptions.query_id = "Identifier of the incoming query, preserved unchanged from the input."; target_output_spec.validation_rules[3] = "query_id and role must be preserved unchanged from the input query"</t>
+  </si>
+  <si>
+    <t>query_id</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.fields = ["query_id", "role", "question", "access_decision", "answer", "citations", "refusal_reason"]; target_output_spec.required_fields includes "query_id"; target_output_spec.field_descriptions.query_id = "Unique identifier for the query, e.g. Q01"</t>
   </si>
   <si>
     <t>EQ1-R11</t>
@@ -528,16 +509,16 @@
     <t>role; required; allowed values employee or manager.</t>
   </si>
   <si>
-    <t>role: str; required; allowed values employee, manager</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.fields[1] = "role"; target_output_spec.field_types.role = "str"; target_output_spec.required_fields includes "role"; target_output_spec.allowed_values.role = ["employee", "manager"]</t>
-  </si>
-  <si>
-    <t>role required; allowed values employee, manager</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.required_fields = ["query_id", "role", "question", "access_decision", "answer", "citations"]; target_output_spec.allowed_values.role = ["employee", "manager"]; target_output_spec.field_descriptions.role = "Role of the user making the query: 'employee' or 'manager'"</t>
+    <t>role: employee | manager</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.field_types.role = "str (enum: employee, manager)"; target_output_spec.allowed_values.role = ["employee", "manager"]</t>
+  </si>
+  <si>
+    <t>role with allowed values employee, manager</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.required_fields includes "role"; target_output_spec.allowed_values.role = ["employee", "manager"]</t>
   </si>
   <si>
     <t>EQ1-R12</t>
@@ -549,16 +530,16 @@
     <t>question; string; required.</t>
   </si>
   <si>
-    <t>question: str; required</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.fields[2] = "question"; target_output_spec.field_types.question = "str"; target_output_spec.required_fields includes "question"; target_output_spec.field_descriptions.question = "The natural-language question as supplied in query_set.json"</t>
-  </si>
-  <si>
-    <t>question required</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.required_fields = ["query_id", "role", "question", "access_decision", "answer", "citations"]; target_output_spec.field_descriptions.question = "The natural-language question asked by the user"</t>
+    <t>question: str</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.field_types.question = "str"; target_output_spec.field_descriptions.question = "The employee's question, preserved unchanged from the input."</t>
+  </si>
+  <si>
+    <t>question</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.fields = ["query_id", "role", "question", "access_decision", "answer", "citations", "refusal_reason"]; target_output_spec.field_descriptions.question = "The natural-language question asked by the user"</t>
   </si>
   <si>
     <t>EQ1-R13</t>
@@ -570,16 +551,16 @@
     <t>access_decision; required; allowed or denied.</t>
   </si>
   <si>
-    <t>access_decision: required; allowed or denied</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.fields[3] = "access_decision"; target_output_spec.required_fields includes "access_decision"; target_output_spec.allowed_values.access_decision = ["allowed", "denied"]</t>
-  </si>
-  <si>
-    <t>access_decision required; allowed or denied</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.required_fields = ["query_id", "role", "question", "access_decision", "answer", "citations"]; target_output_spec.allowed_values.access_decision = ["allowed", "denied"]; target_output_spec.field_descriptions.access_decision = "Whether access was granted: 'allowed' or 'denied'"</t>
+    <t>access_decision: allowed | denied</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.field_types.access_decision = "str (enum: allowed, denied)"; target_output_spec.allowed_values.access_decision = ["allowed", "denied"]</t>
+  </si>
+  <si>
+    <t>access_decision with allowed values allowed, denied</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.required_fields includes "access_decision"; target_output_spec.allowed_values.access_decision = ["allowed", "denied"]</t>
   </si>
   <si>
     <t>EQ1-R14</t>
@@ -591,16 +572,16 @@
     <t>answer; string; required; grounded in authorized retrieved sources.</t>
   </si>
   <si>
-    <t>answer: str; required; cited factual answer grounded only in retrieved content; refusal message when denied</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.fields[4] = "answer"; target_output_spec.field_types.answer = "str"; target_output_spec.required_fields includes "answer"; target_output_spec.field_descriptions.answer = "Cited factual answer grounded only in retrieved content; refusal message when access_decision=denied"</t>
-  </si>
-  <si>
-    <t>answer required; generated answer or refusal message</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.required_fields = ["query_id", "role", "question", "access_decision", "answer", "citations"]; target_output_spec.field_descriptions.answer = "The generated answer, or a refusal message if access is denied"</t>
+    <t>answer: str; grounded answer text or refusal message</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.field_types.answer = "str"; target_output_spec.field_descriptions.answer = "The grounded answer text, or a refusal message when denied or when the authorized sources do not support an answer."; target_output_spec.validation_rules[0] = "An allowed factual answer requires at least one citation to a document permitted for that role"</t>
+  </si>
+  <si>
+    <t>answer; generated answer or refusal message if access is denied</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.required_fields includes "answer"; target_output_spec.field_descriptions.answer = "The generated answer, or a refusal message if access is denied"</t>
   </si>
   <si>
     <t>EQ1-R15</t>
@@ -612,16 +593,16 @@
     <t>citations; required list; at least one for an allowed factual answer and empty for a denied answer.</t>
   </si>
   <si>
-    <t>citations: required list; empty list when access_decision=denied; allowed factual answers include at least one citation</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.fields[5] = "citations"; target_output_spec.field_types.citations = "list"; target_output_spec.required_fields includes "citations"; target_output_spec.field_descriptions.citations = "List of [file_name, page_number] pairs (1-based integer); empty list when access_decision=denied"; target_output_spec.validation_rules includes "citations must be an empty list when access_decision=denied" and "allowed factual answers must include at least one citation to a document permitted for that role"</t>
-  </si>
-  <si>
-    <t>citations required list; at least one for allowed factual answers; empty for denied</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.required_fields = ["query_id", "role", "question", "access_decision", "answer", "citations"]; target_output_spec.field_descriptions.citations = "List of [file_name, page_number] pairs citing source material. Empty list for denied queries."; target_output_spec.validation_rules = ["access_decision must be 'allowed' or 'denied'", "Allowed factual answers require at least one citation", "Each citation must be a two-element list [string file_name, integer page_number] with 1-based page number", "Denied answers require refusal_reason, empty citations list, and must not reveal restricted content", "Do not answer from model memory when authorized evidence is absent"]</t>
+    <t>citations: supporting [file_name, page_number] pairs; empty when denied</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.field_descriptions.citations = "Supporting citations as [file_name, page_number] pairs; empty when denied."; target_output_spec.validation_rules[1] = "A denied answer requires an empty citations list, a non-null refusal_reason, and must not reveal restricted facts"</t>
+  </si>
+  <si>
+    <t>citations required; empty for denied; at least one for allowed factual answers</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.required_fields includes "citations"; target_output_spec.field_descriptions.citations = "List of [file_name, page_number] pairs citing source material. Empty list for denied queries."; target_output_spec.validation_rules includes "Allowed factual answers require at least one citation" and "Denied answers require refusal_reason, empty citations list, and must not reveal restricted content"</t>
   </si>
   <si>
     <t>EQ1-R16</t>
@@ -633,13 +614,16 @@
     <t>file_name; string; first element of every [file_name, page_number] citation pair.</t>
   </si>
   <si>
-    <t>citation first element is file_name</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.field_descriptions.citations = "List of [file_name, page_number] pairs (1-based integer)..."; target_output_spec.validation_rules includes "each citation must be exactly [str, int] (filename, 1-based page number)"</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.field_descriptions.citations = "List of [file_name, page_number] pairs citing source material. Empty list for denied queries."; workflow.steps[1].parameters.citation_format = "[file_name, page_number]"; FILE generated_package\poc\run_poc.py build_citations(): "citations.append([file_name, page_number])"</t>
+    <t>file_name is first element of each citation pair</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.field_types.citations = "list of [file_name: str, page_number: int (1-based)]"; target_output_spec.validation_rules[2] = "Each citation is a two-element list [file_name (str), page_number (1-based int)], in that order"</t>
+  </si>
+  <si>
+    <t>file_name is first element of citation pair</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.field_descriptions.citations = "List of [file_name, page_number] pairs citing source material. Empty list for denied queries."</t>
   </si>
   <si>
     <t>EQ1-R17</t>
@@ -651,16 +635,13 @@
     <t>page_number; 1-based integer; second element of every [file_name, page_number] citation pair.</t>
   </si>
   <si>
-    <t>citation second element is 1-based page_number integer</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.field_descriptions.citations = "List of [file_name, page_number] pairs (1-based integer)..."; target_output_spec.validation_rules includes "each citation must be exactly [str, int] (filename, 1-based page number)"; technical_spec.input_formats[0] = "PDF (text-based, 1-based page numbers)"</t>
-  </si>
-  <si>
-    <t>citation second element is 1-based integer page_number</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.validation_rules includes "Each citation must be a two-element list [string file_name, integer page_number] with 1-based page number"; workflow.steps[1].parameters.citation_page_type = "1-based integer"; FILE generated_package\poc\run_poc.py build_citations(): "page_number = int(page_raw)" and "citations.append([file_name, page_number])"</t>
+    <t>page_number is second element of each citation pair; 1-based int</t>
+  </si>
+  <si>
+    <t>page_number is second element; 1-based integer</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT workflow.steps[1].parameters.citation_page_type = "1-based integer"; target_output_spec.validation_rules includes "Each citation must be a two-element list [string file_name, integer page_number] with 1-based page number"</t>
   </si>
   <si>
     <t>EQ1-R18</t>
@@ -672,16 +653,16 @@
     <t>refusal_reason; required when access_decision is denied; otherwise optional or null.</t>
   </si>
   <si>
-    <t>refusal_reason optional field; required non-null when access_decision=denied; null otherwise</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.optional_fields = ["refusal_reason"]; target_output_spec.field_descriptions.refusal_reason = "Required (non-null) when access_decision=denied; must not reveal restricted facts; null otherwise"; target_output_spec.validation_rules includes "refusal_reason must be non-null when access_decision=denied"</t>
-  </si>
-  <si>
-    <t>refusal_reason optional in schema; described as required when access_decision is denied</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.optional_fields = ["refusal_reason"]; target_output_spec.field_descriptions.refusal_reason = "Required when access_decision is 'denied'; explains why access was refused. Null for allowed queries."; target_output_spec.validation_rules includes "Denied answers require refusal_reason, empty citations list, and must not reveal restricted content"</t>
+    <t>refusal_reason: str | null; explanation for denied or not-found answer; null when allowed and fully supported</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.field_types.refusal_reason = "str | null"; target_output_spec.field_descriptions.refusal_reason = "Explanation for a denied or not-found answer; null when access_decision is allowed and the answer is fully supported."</t>
+  </si>
+  <si>
+    <t>refusal_reason optional field; required when access_decision is denied</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.optional_fields = ["refusal_reason"]; target_output_spec.field_descriptions.refusal_reason = "Required when access_decision is 'denied'; explains why access was refused. Null for allowed queries."</t>
   </si>
   <si>
     <t>EQ1-R19</t>
@@ -693,12 +674,12 @@
     <t>Every citation is exactly a two-element list ordered as [file_name, page_number].</t>
   </si>
   <si>
-    <t>each citation exactly [str, int] ordered as [file_name, page_number]</t>
-  </si>
-  <si>
     <t>Each citation is a two-element list [file_name, page_number]</t>
   </si>
   <si>
+    <t>GENERATED BLUEPRINT target_output_spec.validation_rules[2] = "Each citation is a two-element list [file_name (str), page_number (1-based int)], in that order"</t>
+  </si>
+  <si>
     <t>GENERATED BLUEPRINT target_output_spec.validation_rules includes "Each citation must be a two-element list [string file_name, integer page_number] with 1-based page number"; workflow.steps[1].parameters.citation_format = "[file_name, page_number]"</t>
   </si>
   <si>
@@ -714,16 +695,16 @@
     <t>scripted_answers.json; fixtures/poc_input/query_set.json</t>
   </si>
   <si>
-    <t>All four results returned as separate non-empty parseable JSON objects in output/results.json</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT business_spec.success_criteria[4] = "All four results returned as separate non-empty parseable JSON objects in output/results.json"</t>
-  </si>
-  <si>
-    <t>Process all queries and save JSON array results; four test queries Q01-Q04</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT evaluation.test_queries = [{"id":"Q01"...}, {"id":"Q02"...}, {"id":"Q03"...}, {"id":"Q04"...}]; workflow.steps[2].parameters.format = "json_array"; FILE generated_package\poc\run_poc.py main(): "for q in queries: ... results.append(record)" and writes json.dumps(results, indent=2, ensure_ascii=False)</t>
+    <t>Execute the four role-tagged queries and save JSON results</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_spec.poc_goal = "... execute the four role-tagged queries, and save non-empty parseable JSON results ..."; RELEVANT PoC FILES generated_package\poc\run_poc.py excerpt: "for q in queries:" and "result_path.write_text(json.dumps([r.model_dump() for r in records], indent=2, ensure_ascii=False), ... )"</t>
+  </si>
+  <si>
+    <t>Execute all four role-tagged queries and save JSON results</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_spec.poc_goal = "... Pass all four role-tagged queries (Q01-Q04) ..."; technical_spec.evaluation_requirements = "Four role-tagged queries (Q01-Q04) ..."; RELEVANT PoC FILE generated_package\poc\run_poc.py excerpt: "for q in queries:" ... "results.append(record)"</t>
   </si>
   <si>
     <t>EQ1-R21</t>
@@ -735,16 +716,16 @@
     <t>Use only retrieved content allowed for the user's role and cite every material factual claim.</t>
   </si>
   <si>
-    <t>grounding_policy retrieved_content_only; allowed factual answers must cite permitted documents only</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT workflow.steps[3].parameters.grounding_policy = "retrieved_content_only"; target_output_spec.field_descriptions.answer = "Cited factual answer grounded only in retrieved content..."; target_output_spec.validation_rules includes "allowed factual answers must include at least one citation to a document permitted for that role"</t>
-  </si>
-  <si>
-    <t>Role filter before similarity retrieval; do not answer from model memory when authorized evidence absent</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.security_constraints = "Role filter applied before similarity retrieval so only chunks where allowed_roles contains the query role are candidates."; target_output_spec.validation_rules includes "Do not answer from model memory when authorized evidence is absent"; workflow.steps[1].parameters.no_speculation = true</t>
+    <t>Answer using only authorized retrieved context; cite material factual claims; do not answer from model memory</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.validation_rules[4] = "Cite every material factual claim using [file_name, page_number]"; target_output_spec.validation_rules[5] = "Do not answer from model memory when authorized evidence is absent"; RELEVANT PoC FILES generated_package\poc\run_poc.py ANSWER_PROMPT = "Answer the question using ONLY the information in the context below. Do not use any outside knowledge and do not guess."</t>
+  </si>
+  <si>
+    <t>Role filter applied before similarity retrieval; no answer from model memory when authorized evidence is absent</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.security_constraints = "Role filter applied before similarity retrieval so only chunks where allowed_roles contains the query role are candidates."; target_output_spec.validation_rules includes "Do not answer from model memory when authorized evidence is absent"</t>
   </si>
   <si>
     <t>EQ1-R22</t>
@@ -759,13 +740,13 @@
     <t>If authorized sources do not support an answer, state information was not found and do not speculate</t>
   </si>
   <si>
-    <t>GENERATED BLUEPRINT target_output_spec.missing_value_policy = "If authorized sources do not support an answer, state the information was not found and do not speculate. Do not fabricate citations."; workflow.steps[3].parameters.no_support_policy = "state_not_found_do_not_speculate"; FILE generated_package\poc\prompts\extraction_requirements.md = "If a field cannot be determined, apply this policy: If authorized sources do not support an answer, state the information was not found and do not speculate. Do not fabricate citations."</t>
-  </si>
-  <si>
-    <t>No speculation; not-found message when no authorized content supports query</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT workflow.steps[1].parameters.no_speculation = true; business_spec.poc_goal = "... graceful not-found response when no authorized content supports the query."; FILE generated_package\poc\run_poc.py process_query(): when no documents, answer = "The information was not found in the documents authorised for your role."</t>
+    <t>GENERATED BLUEPRINT target_output_spec.missing_value_policy = "If the authorized sources do not support an answer, state that the information was not found and do not speculate. ..."; RELEVANT PoC FILES generated_package\poc\run_poc.py ANSWER_PROMPT = "If the context does not contain enough information to answer, say plainly that the information was not found in the documents you have access to."</t>
+  </si>
+  <si>
+    <t>No speculation; not-found response when authorized content does not support the query</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT workflow.steps[1].parameters.no_speculation = true; business_spec.poc_goal = "... graceful not-found response when no authorized content supports the query."</t>
   </si>
   <si>
     <t>EQ1-R23</t>
@@ -777,16 +758,16 @@
     <t>Identify the conflict and cite both authorized sources rather than silently choosing one.</t>
   </si>
   <si>
-    <t>If passages contradict each other, state the conflict clearly and cite both</t>
-  </si>
-  <si>
-    <t>FILE generated_package\poc\run_poc.py _SYSTEM_PROMPT excerpt = "CONFLICT HANDLING\n  If passages contradict each other, state the conflict clearly and cite both."</t>
+    <t>If sources conflict, identify the conflict and cite both sources</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.missing_value_policy = "If sources conflict, identify the conflict and cite both sources. Never fabricate a citation."; RELEVANT PoC FILES generated_package\poc\run_poc.py ANSWER_PROMPT = "If different parts of the context disagree, point out the disagreement and mention both sources by name."</t>
   </si>
   <si>
     <t>NOT FOUND</t>
   </si>
   <si>
-    <t>Searched GENERATED BLUEPRINT technical_spec.evaluation_requirements, prompts, workflow.steps, target_output_spec.validation_rules, business_spec.risks; searched FILE generated_package\poc\run_poc.py and generated_package\poc\config.yaml. No explicit conflicting-source policy located.</t>
+    <t>Searched GENERATED BLUEPRINT technical_spec.evaluation_requirements, workflow.steps[*].parameters, target_output_spec.validation_rules, prompts, and conversation lines L0188-L0190, L0317-L0383. No explicit conflicting-source policy stating to identify conflicts and cite both sources was found.</t>
   </si>
   <si>
     <t>EQ1-R24</t>
@@ -798,16 +779,16 @@
     <t>Do not fabricate citations or cite documents not retrieved for the authorized role.</t>
   </si>
   <si>
-    <t>Do not fabricate citations; only cite sources that appear in retrieved passages; validated citations map to retrieved chunks</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.missing_value_policy = "...Do not fabricate citations."; FILE generated_package\poc\run_poc.py _SYSTEM_PROMPT excerpt = "NO EXTRA CITATIONS\n  Only cite sources that appear in the passages below. Do not invent citations."; FILE generated_package\poc\run_poc.py _extract_validated_citations docstring = "Only returns citations that map to an actually retrieved chunk, preventing fabricated or hallucinated citations."</t>
-  </si>
-  <si>
-    <t>must not reveal restricted content; role-filtered retrieval; citation pairs from retrieved documents</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.validation_rules includes "Denied answers require refusal_reason, empty citations list, and must not reveal restricted content" and "Do not answer from model memory when authorized evidence is absent"; technical_spec.security_constraints = "Management-confidential documents ... are never retrieved or disclosed to users with the 'employee' role."; FILE generated_package\poc\run_poc.py build_citations() builds citations from "documents" returned by retrieval</t>
+    <t>Never fabricate a citation; citations reference only role-authorized documents</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.missing_value_policy = "... Never fabricate a citation."; target_output_spec.validation_rules[1] = "A denied answer requires an empty citations list, a non-null refusal_reason, and must not reveal restricted facts"; target_output_spec.validation_rules[5] = "Do not answer from model memory when authorized evidence is absent"; target_output_spec.validation_rules[0] = "An allowed factual answer requires at least one citation to a document permitted for that role"</t>
+  </si>
+  <si>
+    <t>Citations reference only role-authorized documents; no fabricated citations</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.validation_rules includes "Citations empty when denied; citations reference only role-authorized documents; each citation is [filename, page_number]" and "Do not answer from model memory when authorized evidence is absent"</t>
   </si>
   <si>
     <t>EQ1-R25</t>
@@ -819,10 +800,16 @@
     <t>Employees use a web application to sign in, ask natural-language questions, and receive answers with clickable source citations.</t>
   </si>
   <si>
-    <t>Searched GENERATED BLUEPRINT technical_spec.runtime_interface = "cli"; business_spec.user_interface not present; business_process.manual_steps = []; workflow.steps[0].name = "Load PoC input bundle via CLI". No wizard evidence of a web application, sign-in flow, or clickable source citations.</t>
-  </si>
-  <si>
-    <t>Searched GENERATED BLUEPRINT technical_spec.runtime_interface = "cli", runtime.interface = "cli", business_spec.user_interface (absent), business_process.manual_steps = [], workflow.steps. No web application / sign-in / clickable citations description found.</t>
+    <t>Web interface is out of scope for first PoC</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_spec.poc_goal = "Out of scope for this first PoC: a web interface..."; conversation L0190: "A web interface ... [is] outside the first PoC."</t>
+  </si>
+  <si>
+    <t>Web interface outside first PoC</t>
+  </si>
+  <si>
+    <t>Conversation L0190: "A web interface, live repository connector, enterprise sign-in, and numerical RAG-quality threshold are outside the first PoC."</t>
   </si>
   <si>
     <t>EQ1-R26</t>
@@ -834,16 +821,16 @@
     <t>The application uses the signed-in employee's assigned role to filter documents before retrieval.</t>
   </si>
   <si>
-    <t>role from trusted request metadata; pre-retrieval RBAC filters to role-permitted chunks</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.security_constraints[0] = "RBAC pre-filter: role from trusted request metadata (not inferred from question); access_manifest.json maps documents to allowed_roles; unauthorized chunks must never enter model context"; workflow.steps[2].parameters.role_source = "trusted_request_metadata"; workflow.steps[2].parameters.filter_timing = "pre_retrieval"</t>
-  </si>
-  <si>
-    <t>Role supplied with each query; role filter applied before similarity retrieval</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.security_constraints = "Role is trusted request metadata supplied with each query and must never be inferred from question content. Role filter applied before similarity retrieval so only chunks where allowed_roles contains the query role are candidates."; workflow.steps[1].parameters.role_source = "query_metadata" and role_filter_field = "allowed_roles"</t>
+    <t>Requesting role is trusted metadata and access filtering occurs before retrieval</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.security_constraints = "The requesting role is trusted request metadata and must not be inferred from the question text."; technical_spec.security_constraints = "Role-based access filtering must occur before retrieval..."; workflow.steps[3].parameters.access_control = "... ask() is called with filters={'role_&lt;requesting_role&gt;': true} so unauthorized chunks are excluded from the similarity search itself ..."</t>
+  </si>
+  <si>
+    <t>Role is trusted request metadata; role filter applied before similarity retrieval</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.security_constraints = "Role is trusted request metadata supplied with each query and must never be inferred from question content. Role filter applied before similarity retrieval..."; workflow.steps[1].parameters.role_source = "query_metadata"</t>
   </si>
   <si>
     <t>EQ1-R27</t>
@@ -855,13 +842,16 @@
     <t>No routine human reviewer approves or returns each answer.</t>
   </si>
   <si>
-    <t>human_review false; reviewers empty</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.human_review = false; technical_spec.human_review_required = false; business_spec.reviewers = []</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.human_review = false; technical_spec.human_review_required = false; business_spec.reviewers = []; validation.human_review_required = false</t>
+    <t>human_review: no / false</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.human_review = "no"; technical_spec.human_review_required = false; validation.human_review_required = false</t>
+  </si>
+  <si>
+    <t>human_review false</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.human_review = false; technical_spec.human_review_required = false; validation.human_review_required = false</t>
   </si>
   <si>
     <t>EQ1-R28</t>
@@ -873,16 +863,16 @@
     <t>The PoC reads the supplied local poc_input_bundle.json and resolves its documents, access manifest, and query set relative to the bundle; a live repository connector is outside PoC scope.</t>
   </si>
   <si>
-    <t>local file bundle resolved relative to poc_input_bundle.json at runtime</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.data_sources[0] = "local file bundle resolved relative to poc_input_bundle.json at runtime"; workflow.steps[0].parameters.path_resolution = "all other files resolved relative to poc_input_bundle.json"; business_spec.poc_goal includes "CLI: python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;"</t>
-  </si>
-  <si>
-    <t>Reads local poc_input_bundle.json; resolves documents/access manifest/query set relative to bundle; no integration targets</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.data_sources = ["local_file_bundle"]; technical_spec.integration_targets = []; workflow.steps[0].parameters.description = "User provides path to poc_input_bundle.json via CLI. All referenced files (PDFs, access_manifest.json, query_set.json) are resolved relative to the bundle file."; FILE generated_package\poc\run_poc.py Usage: "python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;" and main(): resolves bundle["access_manifest"], bundle["query_set"], bundle["documents_directory"] relative to bundle_dir</t>
+    <t>PoC uses local poc_input_bundle.json and resolves access_manifest.json, query_set.json, and PDFs relative to the bundle; live repository out of scope</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.data_sources = "PoC uses a local fixture bundle: three sample PDFs ... plus access_manifest.json and query_set.json, all resolved relative to poc_input_bundle.json. Connection to a live enterprise document repository is out of scope for this PoC."; RELEVANT PoC FILES generated_package\poc\run_poc.py docstring = "Usage: python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;" and function load_bundle() comment/value = "Load poc_input_bundle.json and resolve the files it points to, all relative to the bundle file's own location"</t>
+  </si>
+  <si>
+    <t>Local supplied bundle; no live repository</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.data_sources = ["local_file_bundle"]; conversation L0156: "The first PoC uses these supplied local inputs; connection to a live document repository is outside its scope."; conversation L0190: "...resolve the other supplied files relative to that bundle..."</t>
   </si>
   <si>
     <t>EQ1-R29</t>
@@ -894,13 +884,16 @@
     <t>Two internal documents are available to employee and manager roles; the Project Aurora strategy is management-confidential and manager-only.</t>
   </si>
   <si>
-    <t>Searched GENERATED BLUEPRINT technical_spec.security_constraints, business_spec.input_artifacts, workflow.steps[1].parameters.metadata_fields, assumptions, artifacts. Found references to classification and allowed_roles metadata, but no explicit wizard statement that two internal documents are available to employee and manager and Project Aurora is manager-only.</t>
-  </si>
-  <si>
-    <t>Project Aurora is management-confidential and manager-only</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.security_constraints = "Management-confidential documents (project_aurora_pricing_strategy.pdf) are never retrieved or disclosed to users with the 'employee' role."; business_spec.input_artifacts includes the three PDFs. No explicit blueprint entry found stating the other two documents are available to both employee and manager.</t>
+    <t>employee_travel_policy.pdf and mx200_maintenance_manual.pdf available to employee+manager; project_aurora_pricing_strategy.pdf manager-only management-confidential</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_spec.input_artifacts = ["internal policies", "equipment manuals", "commercially sensitive management documents"]; business_spec.poc_goal = "... three sample PDFs (employee travel policy, MX-200 maintenance manual, Project Aurora pricing strategy) ..."; conversation L0078: "The travel policy and maintenance manual are available to employee and manager roles. The Project Aurora strategy is management-confidential and available only to the manager role."</t>
+  </si>
+  <si>
+    <t>Travel policy and maintenance manual for employee+manager; Project Aurora manager only / management-confidential</t>
+  </si>
+  <si>
+    <t>Conversation L0078: "The travel policy and maintenance manual are available to employee and manager roles. The Project Aurora strategy is management-confidential and available only to the manager role."; GENERATED BLUEPRINT business_spec.input_artifacts line item text includes "project_aurora_pricing_strategy.pdf" and business_spec.stakeholders/intended_users reflect roles.</t>
   </si>
   <si>
     <t>EQ1-R30</t>
@@ -912,16 +905,16 @@
     <t>Filter by allowed roles before retrieval so unauthorized chunks never enter the model context.</t>
   </si>
   <si>
-    <t>RBAC pre-filter before retrieval; unauthorized chunks must never enter model context</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.security_constraints[0] = "RBAC pre-filter... unauthorized chunks must never enter model context"; workflow.steps[2].name = "Apply RBAC pre-filter and retrieve top-4 eligible chunks per query"; workflow.steps[2].parameters.filter_timing = "pre_retrieval"</t>
+    <t>Role-based access filtering must occur before retrieval; unauthorized chunks never enter model context</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.security_constraints = "Role-based access filtering must occur before retrieval, so unauthorized chunks never enter the model's context window."; workflow.steps[3].parameters.access_control = "Pre-retrieval RBAC ... unauthorized chunks are excluded from the similarity search itself ..., never entering the model context."</t>
   </si>
   <si>
     <t>Role filter applied before similarity retrieval</t>
   </si>
   <si>
-    <t>GENERATED BLUEPRINT technical_spec.security_constraints = "Role filter applied before similarity retrieval so only chunks where allowed_roles contains the query role are candidates."; workflow.steps[1].parameters.role_filter_field = "allowed_roles"</t>
+    <t>GENERATED BLUEPRINT technical_spec.security_constraints = "Role filter applied before similarity retrieval so only chunks where allowed_roles contains the query role are candidates."; conversation L0078: "Access filtering must happen before retrieval so unauthorized chunks never enter the model context."</t>
   </si>
   <si>
     <t>EQ1-R31</t>
@@ -933,16 +926,16 @@
     <t>Refuse without exposing restricted facts or citations.</t>
   </si>
   <si>
-    <t>answer must not reveal restricted content when denied; citations empty when denied</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.validation_rules includes "answer must not reveal restricted content when access_decision=denied" and "citations must be an empty list when access_decision=denied"; target_output_spec.field_descriptions.refusal_reason = "...must not reveal restricted facts..."</t>
-  </si>
-  <si>
-    <t>Denied answers require empty citations and must not reveal restricted content</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.validation_rules includes "Denied answers require refusal_reason, empty citations list, and must not reveal restricted content"; technical_spec.evaluation_requirements = "Q03 (employee, Project Aurora ceiling): access=denied, empty citations, no 12%/22%/CFO details."; FILE generated_package\poc\run_poc.py process_query(): denied answer returns citations = [] and generic denial text</t>
+    <t>Denied answers must not reveal restricted facts or citations</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.security_constraints = "Denied answers must not reveal restricted facts or citations."; target_output_spec.validation_rules[1] = "A denied answer requires an empty citations list, a non-null refusal_reason, and must not reveal restricted facts"</t>
+  </si>
+  <si>
+    <t>Denied answers require refusal_reason, empty citations, and must not reveal restricted content</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.validation_rules includes "Denied answers require refusal_reason, empty citations list, and must not reveal restricted content"</t>
   </si>
   <si>
     <t>EQ1-R32</t>
@@ -954,16 +947,16 @@
     <t>External model APIs are allowed; fixtures contain no personal data; no exact retention period is specified; enterprise identity and full audit service are outside PoC scope.</t>
   </si>
   <si>
-    <t>Cloud LLM API calls to Azure OpenAI are permitted; no personal data in synthetic PoC fixtures; no audit-log service required; enterprise identity integration out of scope; retention_policy not_specified</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.security_constraints = ["RBAC pre-filter...", "Cloud LLM API calls to Azure OpenAI are permitted", "No personal data in synthetic PoC fixtures", "No audit-log service required for PoC; enterprise identity integration is out of PoC scope"]; governance.data_handling.retention_policy = "not_specified"</t>
-  </si>
-  <si>
-    <t>external_model_api_allowed true; retention_policy not_specified; contains_personal_data unknown/assumed none; audit_log_required false</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT governance.data_handling.external_model_api_allowed = true; governance.data_handling.retention_policy = "not_specified"; governance.data_handling.contains_personal_data = "unknown"; governance.data_handling.audit_log_required = false; assumptions[4].text = "The documents are assumed not to contain personal data..."; technical_spec.integration_targets = []</t>
+    <t>External model APIs allowed; fixtures contain no personal data; no exact retention period specified; enterprise identity and full audit-log service out of scope</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.security_constraints = "External model APIs are allowed. The synthetic PoC fixtures contain no personal data. Enterprise identity integration and a full audit-log service are out of scope for the PoC ... No exact data-retention period was specified."</t>
+  </si>
+  <si>
+    <t>External model API allowed; retention not_specified; contains_personal_data unknown</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT governance.data_handling.external_model_api_allowed = true; governance.data_handling.retention_policy = "not_specified"; governance.data_handling.contains_personal_data = "unknown"; assumptions[4].text = "The documents are assumed not to contain personal data..."</t>
   </si>
   <si>
     <t>EQ1-R33</t>
@@ -975,16 +968,16 @@
     <t>Command-line PoC supports python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;, executes the fixed query set, and writes JSON results.</t>
   </si>
   <si>
-    <t>CLI supports python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;; output/results.json</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.runtime_entrypoint = "python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;"; technical_spec.runtime_interface = "cli"; workflow.steps[3].parameters.output_path = "output/results.json"; FILE generated_package\poc\run_poc.py header Usage = "python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;" and Output = "output/results.json — list of RAGAnswerRecord objects."</t>
-  </si>
-  <si>
-    <t>CLI: python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;; writes JSON results</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT runtime.entrypoint = "poc/run_poc.py"; workflow.steps[0].parameters.entrypoint_flag = "--input"; technical_spec.runtime_interface = "cli"; FILE generated_package\poc\run_poc.py Usage: "python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;" and writes to output/results.json with json.dumps(results, indent=2, ensure_ascii=False)</t>
+    <t>CLI: python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;; saves JSON results</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.runtime_interface = "CLI: `python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;`, resolving access_manifest.json, query_set.json, and the documents directory relative to that bundle file."; RELEVANT PoC FILES generated_package\poc\run_poc.py argparse adds "--input" required=True; run_poc.py writes output to result_path = output_dir / "answer_records.json"</t>
+  </si>
+  <si>
+    <t>CLI python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;; writes JSON results</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.runtime_interface = "cli"; workflow.steps[0].parameters.entrypoint_flag = "--input"; RELEVANT PoC FILE generated_package\poc\run_poc.py docstring/usage: "python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;" and output_path = output_dir / "results.json"</t>
   </si>
   <si>
     <t>EQ1-R34</t>
@@ -996,13 +989,16 @@
     <t>Employees, managers, and knowledge owners are internal participants; no external party is required for the fixture workflow.</t>
   </si>
   <si>
-    <t>Searched GENERATED BLUEPRINT business_process.participants = []; business_process.external_parties = []; business_spec.intended_users = ["employee", "manager", "knowledge_owner"]; business_spec.stakeholders = ["knowledge_owners", "managers", "IT"]. Internal roles are mentioned, but no explicit wizard value states these are the participants and that no external party is required for the fixture workflow.</t>
-  </si>
-  <si>
-    <t>participants: employee, manager, GAIK AI System; external_parties: []</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT business_process.participants = [{"id":"employee","name":"Employee","kind":"human_role"}, {"id":"manager","name":"Manager","kind":"human_role"}, {"id":"gaik_ai_system","name":"GAIK AI System","kind":"human_role"}]; business_process.external_parties = []; business_spec.stakeholders = ["employees", "managers", "knowledge_owners"]</t>
+    <t>Participants: Employee / Manager; no external parties</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_process.participants[0] = {"id": "requesting_user", "name": "Employee / Manager", "kind": "human_role", "default_lane_for": ["user_task"]}; business_process.external_parties = []</t>
+  </si>
+  <si>
+    <t>Participants: employee, manager, gaik_ai_system; external_parties: []</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_process.participants = [{"id":"employee"...},{"id":"manager"...},{"id":"gaik_ai_system"...}]; business_process.external_parties = []</t>
   </si>
   <si>
     <t>EQ1-R35</t>
@@ -1014,16 +1010,16 @@
     <t>Faster reliable answers with citations and correct access behavior, plus successful execution over the fixture; no numerical improvement threshold.</t>
   </si>
   <si>
-    <t>Success includes cited reliable answers, correct access behavior, fixture execution over Q01-Q04, no numerical threshold specified</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT business_spec.success_criteria includes Q01-Q04 expected outcomes and "All four results returned as separate non-empty parseable JSON objects in output/results.json"; technical_spec.evaluation_requirements.numerical_threshold = "not_specified"; business_spec.expected_value includes faster reliable answers with citations and access protection semantics</t>
-  </si>
-  <si>
-    <t>Reliable faster answers with citations and correct access behavior; fixture execution over four queries; no numeric threshold</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT business_spec.success_criteria = ["Employees find reliable answers faster than manual search", "Answers are verifiable through document citations", "Employees never receive content outside their authorized role", "System correctly refuses to answer from unauthorized content"]; technical_spec.evaluation_requirements = "Four role-tagged queries (Q01-Q04) with exact expected access decisions, answer content, and citation pairs..."</t>
+    <t>Reliable answers faster, citations, no out-of-role content, deterministic four-query acceptance test; no numerical threshold</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_spec.success_criteria = "Employees find reliable answers faster, can verify answers through citations, and never receive content outside their role. No numerical time-saving, accuracy, cost, or adoption target was specified."; technical_spec.evaluation_requirements = "Deterministic acceptance test using the four supplied role-tagged queries (Q01-Q04) ... No numerical RAG-quality threshold ... was specified for the first PoC."</t>
+  </si>
+  <si>
+    <t>Reliable answers faster than manual search, citations, no out-of-role content; no numerical quality threshold</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_spec.success_criteria = ["Employees find reliable answers faster than manual search", "Answers are verifiable through document citations", "Employees never receive content outside their authorized role", "System correctly refuses to answer from unauthorized content"]; technical_spec.evaluation_requirements ends with "no numerical quality threshold"</t>
   </si>
   <si>
     <t>EQ1-R36</t>
@@ -1032,13 +1028,16 @@
     <t>Model configuration</t>
   </si>
   <si>
-    <t>GENERATED BLUEPRINT technical_spec.model_provider = "azure_openai"; technical_spec.model_preferences.answer_model = "gpt-5.4"; technical_spec.model_preferences.temperature = 0.0; technical_spec.model_preferences.reasoning_effort = "medium"; technical_spec.model_preferences.embedding_model = "from_env_AZURE_EMBEDDING_DEPLOYMENT"; FILE generated_package\poc\config.yaml models.embedding = "text-embedding-3-large"</t>
-  </si>
-  <si>
-    <t>azure_openai; generation_model gpt-5.4; temperature 1.0; reasoning_effort medium; embedding_model ${AZURE_OPENAI_EMBEDDING_DEPLOYMENT}</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.model_provider = "azure_openai"; technical_spec.model_preferences = {"generation_model":"gpt-5.4","temperature":1.0,"reasoning_effort":"medium","embedding_model":"${AZURE_OPENAI_EMBEDDING_DEPLOYMENT}"}; models = {"provider":"azure_openai","answer_model":"gpt-5.4","embedding_model":"${AZURE_OPENAI_EMBEDDING_DEPLOYMENT}","temperature":1.0,"reasoning_effort":"medium"}; FILE generated_package\poc\config.yaml models.extraction = gpt-5.4 and models.temperature = 1.0</t>
+    <t>Azure OpenAI; generation model gpt-5.4; reasoning_effort medium; embedding model from Azure OpenAI env setting; temperature 1.0 in blueprint/PoC</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.model_provider = "azure_openai"; technical_spec.model_preferences.generation_model = "gpt-5.4"; technical_spec.model_preferences.temperature = 1.0; technical_spec.model_preferences.reasoning_effort = "medium"; technical_spec.model_preferences.embedding_model = "Azure OpenAI embedding deployment supported by RAGWorkflow; exact deployment name is an environment setting"; RELEVANT PoC FILES generated_package\poc\config.yaml models.generation = gpt-5.4, models.temperature = 1.0, models.reasoning_effort = medium</t>
+  </si>
+  <si>
+    <t>Azure OpenAI; gpt-5.4; reasoning_effort medium; embedding model via env var; temperature 1.0 in blueprint/config</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.model_provider = "azure_openai"; technical_spec.model_preferences.generation_model = "gpt-5.4"; technical_spec.model_preferences.reasoning_effort = "medium"; technical_spec.model_preferences.embedding_model = "${AZURE_OPENAI_EMBEDDING_DEPLOYMENT}"; technical_spec.model_preferences.temperature = 1.0; RELEVANT PoC FILE generated_package\poc\config.yaml models.extraction = gpt-5.4 and models.temperature = 1.0</t>
   </si>
   <si>
     <t>EQ1-R37</t>
@@ -1050,13 +1049,13 @@
     <t>Hallucinated answers, wrong citations, restricted retrieval or leakage, stale documents, and answering without authorized support.</t>
   </si>
   <si>
-    <t>Hallucinated/speculative answers, fabricated/incorrect citations, unauthorized chunk leakage, restricted facts disclosed on denied query, stale documents, unsupported answers</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT business_spec.risks = ["Hallucinated or speculative answers not grounded in retrieved content", "Fabricated or incorrect citations", "Unauthorized chunk leakage into model context via pre-filter bypass", "Restricted facts disclosed in answer text on a denied query", "Stale documents producing outdated answers", "Answer returned when no authorized source supports the claim"]</t>
-  </si>
-  <si>
-    <t>Hallucinated answers, wrong citations, restricted retrieval/leakage, stale docs, speculative unsupported answers</t>
+    <t>Hallucinated answers, fabricated/incorrect citations, restricted retrieval, leakage, stale documents, unsupported answer generation</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_spec.risks = ["hallucinated answers", "fabricated or incorrect citations", "retrieval of restricted chunks into the model context", "leakage of restricted content through answer text or citations", "stale or outdated source documents", "returning an answer when the authorized collection contains no support"]</t>
+  </si>
+  <si>
+    <t>Hallucinated answers, incorrect citations, restricted retrieval/leakage, stale documents, unsupported answer generation</t>
   </si>
   <si>
     <t>GENERATED BLUEPRINT business_spec.risks = ["Hallucinated answers not grounded in retrieved content", "Fabricated or incorrect citations", "Retrieval of restricted chunks for unauthorized roles", "Leakage of restricted content through answer text or citations", "Stale documents producing outdated answers", "System returning speculative answer when no authorized source supports the query"]</t>
@@ -1071,13 +1070,13 @@
     <t>Ingest the three supplied documents and run four role-tagged queries, producing grounded cited answers for authorized cases and a non-leaking refusal for the unauthorized case.</t>
   </si>
   <si>
-    <t>Demonstrate role-aware, citation-grounded question answering over three PDF documents; execute all four role-tagged queries (Q01-Q04); save JSON results</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT business_spec.poc_goal = "Demonstrate role-aware, citation-grounded question answering over three PDF documents using a local vector store and trusted role metadata. CLI: python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;. Execute all four role-tagged queries (Q01-Q04) and save non-empty parseable JSON results to output/results.json."</t>
-  </si>
-  <si>
-    <t>Demonstrate role-aware cited Q&amp;A over three PDFs and pass four role-tagged queries with correct access decisions and citation pairs</t>
+    <t>Demonstrate role-aware citation-grounded Q&amp;A over three PDFs using supplied manifest and query set; execute four role-tagged queries; save JSON results with correct access decisions and citations</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_spec.poc_goal = "Demonstrate role-aware, citation-grounded question answering over three sample PDFs ... using a supplied access manifest and query set. Run `python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;`, resolve the other supplied files relative to that bundle, execute the four role-tagged queries, and save non-empty parseable JSON results demonstrating correct access decisions and citations."</t>
+  </si>
+  <si>
+    <t>Role-aware citation-grounded Q&amp;A over three PDFs plus access_manifest/query_set; deny management-confidential content to employees; pass Q01-Q04</t>
   </si>
   <si>
     <t>GENERATED BLUEPRINT business_spec.poc_goal = "Demonstrate role-aware citation-grounded Q&amp;A over three PDFs with access_manifest.json and query_set.json from the supplied input bundle. Prove correct access control (deny management-confidential content to general employees), accurate [filename, page] citations, and graceful not-found response when no authorized content supports the query. Pass all four role-tagged queries (Q01-Q04) with exact expected access decisions and citation pairs."</t>
@@ -1092,16 +1091,16 @@
     <t>Required fields and controlled values are enforced; allowed answers have [file_name, page_number] citations; denied answers have refusal_reason, empty citations, and no restricted facts.</t>
   </si>
   <si>
-    <t>Validation rules enforce required controlled values, citation structure, empty citations and refusal_reason on denied answers, and no restricted content leakage</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.validation_rules = ["access_decision must be 'allowed' or 'denied'", "citations must be an empty list when access_decision=denied", "refusal_reason must be non-null when access_decision=denied", "each citation must be exactly [str, int] (filename, 1-based page number)", "answer must not reveal restricted content when access_decision=denied", "allowed factual answers must include at least one citation to a document permitted for that role", "exact values must be preserved: EUR 180, 250 operating hours, 1,000 operating hours, 1.8 bar, 12 percent, 22 percent"]</t>
-  </si>
-  <si>
-    <t>Validation enforces required fields, controlled values, citation structure, denied-answer refusal_reason/empty citations/no restricted content, no model-memory answering</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.required_fields = ["query_id", "role", "question", "access_decision", "answer", "citations"]; target_output_spec.allowed_values = {"role":["employee","manager"],"access_decision":["allowed","denied"]}; target_output_spec.validation_rules = ["access_decision must be 'allowed' or 'denied'", "Allowed factual answers require at least one citation", "Each citation must be a two-element list [string file_name, integer page_number] with 1-based page number", "Denied answers require refusal_reason, empty citations list, and must not reveal restricted content", "Do not answer from model memory when authorized evidence is absent"]</t>
+    <t>Allowed answer requires citation; denied answer requires empty citations, non-null refusal_reason, and no restricted facts; citation format [file_name, page_number]</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.validation_rules[0] = "An allowed factual answer requires at least one citation to a document permitted for that role"; target_output_spec.validation_rules[1] = "A denied answer requires an empty citations list, a non-null refusal_reason, and must not reveal restricted facts"; target_output_spec.validation_rules[2] = "Each citation is a two-element list [file_name (str), page_number (1-based int)], in that order"</t>
+  </si>
+  <si>
+    <t>Validation rules enforce access_decision values, citation structure, allowed-answer citations, denied-answer refusal_reason/empty citations/no restricted content</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT target_output_spec.validation_rules = ["access_decision must be 'allowed' or 'denied'", "Allowed factual answers require at least one citation", "Each citation must be a two-element list [string file_name, integer page_number] with 1-based page number", "Denied answers require refusal_reason, empty citations list, and must not reveal restricted content", "Do not answer from model memory when authorized evidence is absent"]</t>
   </si>
   <si>
     <t>EQ1-R40</t>
@@ -1113,10 +1112,16 @@
     <t>The intended employee interaction is a web application, while the first PoC may use CLI and JSON output.</t>
   </si>
   <si>
-    <t>Searched GENERATED BLUEPRINT technical_spec.runtime_interface = "cli"; runtime.interface = "cli"; business_spec.poc_goal references CLI and JSON output; business_spec.user_interface not present. No wizard evidence explicitly separating intended employee web interaction from PoC CLI.</t>
-  </si>
-  <si>
-    <t>Searched GENERATED BLUEPRINT technical_spec.runtime_interface = "cli", runtime.interface = "cli", business_spec.poc_goal, use_case.description, business_spec.user_interface (absent). No explicit separation stating final employee interaction is web app while PoC is CLI.</t>
+    <t>Web interface out of scope for first PoC; runtime interface is CLI</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_spec.poc_goal = "Out of scope for this first PoC: a web interface ..."; technical_spec.runtime_interface = "CLI: `python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;` ..."</t>
+  </si>
+  <si>
+    <t>Web interface outside first PoC; CLI for PoC</t>
+  </si>
+  <si>
+    <t>Conversation L0190: "A web interface ... [is] outside the first PoC."; GENERATED BLUEPRINT technical_spec.runtime_interface = "cli"; runtime.interface = "cli"</t>
   </si>
   <si>
     <t>EQ1-R41</t>
@@ -1128,16 +1133,16 @@
     <t>Structure-aware chunks preserve file_name, 1-based page_number, classification, and allowed_roles metadata; role filtering occurs before semantic top-four retrieval; hybrid search or reranking is optional.</t>
   </si>
   <si>
-    <t>structure_aware chunking; metadata file_name/page_number/classification/allowed_roles; pre_retrieval role filtering; top_k 4</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT workflow.steps[1].parameters.chunking_strategy = "structure_aware"; workflow.steps[1].parameters.metadata_fields = ["file_name", "page_number", "classification", "allowed_roles"]; workflow.steps[2].parameters.filter_timing = "pre_retrieval"; workflow.steps[2].parameters.top_k = 4; workflow.steps[2].name = "Apply RBAC pre-filter and retrieve top-4 eligible chunks per query"</t>
-  </si>
-  <si>
-    <t>structure_aware chunks; metadata classification/allowed_roles/file_name/page_number; role filtering before retrieval; top_k 4</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT workflow.steps[1].parameters.chunking_strategy = "structure_aware"; workflow.steps[1].parameters.rbac_metadata_fields = ["classification", "allowed_roles", "file_name", "page_number"]; workflow.steps[1].parameters.role_filter_field = "allowed_roles"; workflow.steps[1].parameters.retriever_top_k = 4; technical_spec.security_constraints = "Role filter applied before similarity retrieval..."</t>
+    <t>Chunks tagged with role_&lt;role&gt; metadata; retriever_top_k 4; pre-retrieval role filter via ask(filters=...); retriever_hybrid false; retriever_rerank false</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT workflow.steps[3].parameters.retriever_top_k = 4; workflow.steps[3].parameters.retriever_hybrid = false; workflow.steps[3].parameters.retriever_rerank = false; workflow.steps[3].parameters.access_control = "Pre-retrieval RBAC: each indexed chunk is tagged with boolean role_&lt;role&gt; metadata flags ... ask() is called with filters={'role_&lt;requesting_role&gt;': true} ..."</t>
+  </si>
+  <si>
+    <t>Metadata fields classification/allowed_roles/file_name/page_number; role filter before retrieval; retriever_top_k 4; structure_aware chunking</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT workflow.steps[1].parameters.rbac_metadata_fields = ["classification", "allowed_roles", "file_name", "page_number"]; workflow.steps[1].parameters.chunking_strategy = "structure_aware"; workflow.steps[1].parameters.retriever_top_k = 4; technical_spec.security_constraints = "Role filter applied before similarity retrieval..."</t>
   </si>
   <si>
     <t>EQ1-R42</t>
@@ -1152,16 +1157,16 @@
     <t>scripted_answers.json; fixtures/expected_rag_results.json</t>
   </si>
   <si>
-    <t>Q01 cite [employee_travel_policy.pdf, 3]; Q02 cite mx200_maintenance_manual.pdf pages 3 and 4; Q03 denied with empty citations and no restricted facts; Q04 12 percent with CFO approval cite [project_aurora_pricing_strategy.pdf, 3]</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT business_spec.success_criteria[0] = "Q01 (employee, Helsinki hotel limit): answers EUR 180 per night with Finance Director approval required when exceeded, citing [employee_travel_policy.pdf, 3]"; success_criteria[1] = "Q02 (employee, MX-200 filter): answers inspection every 250 operating hours and replacement after 1,000 operating hours or 1.8 bar, citing mx200_maintenance_manual.pdf pages 3 and 4"; success_criteria[2] = "Q03 (employee, Project Aurora ceiling): access_decision=denied, empty citations list, no restricted facts disclosed"; success_criteria[3] = "Q04 (manager, Project Aurora ceiling and approver): answers 12 percent ceiling with written CFO approval required above the ceiling, citing [project_aurora_pricing_strategy.pdf, 3]"</t>
-  </si>
-  <si>
-    <t>Q01 allowed cites [employee_travel_policy.pdf,3]; Q02 allowed cites [mx200_maintenance_manual.pdf,3] and [mx200_maintenance_manual.pdf,4]; Q03 denied empty citations no 12%/22%/CFO details; Q04 allowed 12% + CFO approval cites [project_aurora_pricing_strategy.pdf,3]</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.evaluation_requirements = "Four role-tagged queries (Q01-Q04) with exact expected access decisions, answer content, and citation pairs. Q01 (employee, Helsinki hotel limit): access=allowed, EUR 180/night + Finance Director approval, cite [employee_travel_policy.pdf, 3]. Q02 (employee, MX-200 filter): access=allowed, 250h inspection + 1000h or 1.8bar replacement, cite [mx200_maintenance_manual.pdf, 3] and [mx200_maintenance_manual.pdf, 4]. Q03 (employee, Project Aurora ceiling): access=denied, empty citations, no 12%/22%/CFO details. Q04 (manager, Project Aurora ceiling and approver): access=allowed, 12% ceiling + CFO written approval, cite [project_aurora_pricing_strategy.pdf, 3]."; evaluation.test_queries contains matching entries for Q01-Q04</t>
+    <t>Four-query deterministic acceptance test Q01-Q04 with specified required facts/access decision/citation pairs</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.evaluation_requirements = "Deterministic acceptance test using the four supplied role-tagged queries (Q01-Q04), checked against required facts, the exact access decision (allowed/denied), and required citation pairs per query."; conversation L0190 contains detailed Q01-Q04 expected outputs and citations; NOT FOUND for exact values under GENERATED BLUEPRINT evaluation/ground_truth content because no expected_results.json excerpt was provided.</t>
+  </si>
+  <si>
+    <t>Q01/Q02/Q03/Q04 expected role-aware outputs captured in evaluation_requirements and test_queries</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.evaluation_requirements = "Four role-tagged queries (Q01-Q04) with exact expected access decisions, answer content, and citation pairs..."; evaluation.test_queries[0..3] specify Q01 expected_citations [["employee_travel_policy.pdf",3]], Q02 expected_citations [["mx200_maintenance_manual.pdf",3],["mx200_maintenance_manual.pdf",4]], Q03 expected_access_decision "denied" expected_citations [], Q04 expected_citations [["project_aurora_pricing_strategy.pdf",3]]</t>
   </si>
   <si>
     <t>EQ1 Diagnostics</t>
@@ -1182,16 +1187,16 @@
     <t>No SLA, throughput, latency, volume, budget, accuracy, adoption, time-saving, or cost-saving number may be treated as user-confirmed.</t>
   </si>
   <si>
-    <t>No quantified SLA/throughput/latency/volume/budget/accuracy/adoption/time-saving/cost-saving user-confirmed metrics found; evaluation threshold marked not_specified</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.evaluation_requirements.numerical_threshold = "not_specified"; searched business_spec.success_criteria, business_spec.expected_value, technical_spec.model_preferences, assumptions for user-confirmed SLA/throughput/latency/volume/budget/accuracy/adoption/time-saving/cost-saving numbers</t>
-  </si>
-  <si>
-    <t>No SLA, throughput, document volume, latency, or budget targets are specified; such values are recorded as assumptions/defaults.</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT: $.assumptions[5].text = "Valid implementation defaults are recorded as assumptions per user instruction. No SLA, throughput, document volume, latency, or budget targets are specified."; corroborating absence of quantified targets in $.business_spec.success_criteria = ["Employees find reliable answers faster than manual search", "Answers are verifiable through document citations", "Employees never receive content outside their authorized role", "System correctly refuses to answer from unauthorized content"] and $.technical_spec.model_preferences contains no user-confirmed SLA/budget/latency numbers.</t>
+    <t>success criteria recorded qualitatively; no numerical targets specified; assumptions note no numerical success/adoption/time-saving target was specified</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT business_spec.success_criteria = "Employees find reliable answers faster, can verify answers through citations, and never receive content outside their role. No numerical time-saving, accuracy, cost, or adoption target was specified."; GENERATED BLUEPRINT assumptions[0].text = "No numerical success/adoption/time-saving target was specified; success is defined qualitatively (faster reliable answers, verifiable citations, no out-of-role disclosure)."; CONVERSATION L0116-L0118: user says "No numerical time-saving, answer-accuracy, cost, or adoption target is specified."</t>
+  </si>
+  <si>
+    <t>No numerical target is specified; valid implementation defaults may be recorded as assumptions, not user-confirmed requirements.</t>
+  </si>
+  <si>
+    <t>Conversation L0188-L0189: User states "No SLA, throughput, document-volume, latency, or budget target is specified. Valid implementation defaults may be recorded as assumptions, not user-confirmed requirements." Closest blueprint value: $.assumptions[5].text = "Valid implementation defaults are recorded as assumptions per user instruction. No SLA, throughput, document volume, latency, or budget targets are specified." Also related user evidence at L0116: "No numerical time-saving, answer-accuracy, cost, or adoption target is specified."</t>
   </si>
   <si>
     <t>EQ1-D02</t>
@@ -1203,16 +1208,16 @@
     <t>No live repository, enterprise identity, ticketing, or audit-service integration may be treated as required for the PoC.</t>
   </si>
   <si>
-    <t>PoC scope excludes enterprise identity and audit-log service; integration_targets is empty; data source is local file bundle</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.integration_targets = []; technical_spec.security_constraints[3] = "No audit-log service required for PoC; enterprise identity integration is out of PoC scope"; technical_spec.data_sources[0] = "local file bundle resolved relative to poc_input_bundle.json at runtime"</t>
-  </si>
-  <si>
-    <t>Integration scope is local_file_bundle only; no external integration targets are specified.</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT: $.technical_spec.data_sources = ["local_file_bundle"]; $.technical_spec.integration_targets = []; $.technical_spec.runtime_interface = "cli"; $.business_spec.poc_goal = "Demonstrate role-aware citation-grounded Q&amp;A over three PDFs with access_manifest.json and query_set.json from the supplied input bundle...". PoC file corroboration: generated_package\poc\run_poc.py docstring = "Reads queries from a supplied input bundle... and writes RAGAnswerRecord results to output/results.json."</t>
+    <t>integration targets empty; live repository connector, enterprise sign-in/identity integration, and full audit-log service are out of scope for the PoC</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.integration_targets = []; GENERATED BLUEPRINT business_spec.poc_goal = "... Out of scope for this first PoC: a web interface, a live document-repository connector, enterprise sign-in/identity integration, a full audit-log service, and a numerical RAG-quality threshold."; GENERATED BLUEPRINT technical_spec.data_sources = "... Connection to a live enterprise document repository is out of scope for this PoC."; CONVERSATION L0188-L0190: user says "A web interface, live repository connector, enterprise sign-in, and numerical RAG-quality threshold are outside the first PoC."</t>
+  </si>
+  <si>
+    <t>Integration targets are none/out of scope; local input bundle only, no live repository.</t>
+  </si>
+  <si>
+    <t>Blueprint $.technical_spec.integration_targets = []; $.business_spec.input_artifacts = ["employee_travel_policy.pdf","mx200_maintenance_manual.pdf","project_aurora_pricing_strategy.pdf","access_manifest.json","query_set.json","poc_input_bundle.json"]; $.technical_spec.data_sources = ["local_file_bundle"]. Conversation L0156-L0158: "The first PoC uses these supplied local inputs; connection to a live document repository is outside its scope." Conversation L0190: "A web interface, live repository connector, enterprise sign-in, and numerical RAG-quality threshold are outside the first PoC."</t>
   </si>
   <si>
     <t>EQ1-D03</t>
@@ -1224,16 +1229,16 @@
     <t>Chunk size, overlap, embedding deployment name, vector database brand, and environment details not explicitly fixed must be assumptions or defaults.</t>
   </si>
   <si>
-    <t>Chunking and embedding deployment are marked as assumptions/defaults in blueprint, but PoC files set concrete defaults: chunk_size 400, overlap 80, embedding text-embedding-3-large</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT assumptions[2].text = "Structure-aware chunking uses paragraph or section boundaries with moderate overlap (approximately 10-20% of chunk size). Exact chunk size defaults to approximately 512 tokens."; GENERATED BLUEPRINT assumptions[3].text = "The Azure OpenAI embedding deployment name is provided via environment variable AZURE_EMBEDDING_DEPLOYMENT. The specific model name is not user-confirmed."; FILE generated_package\poc\run_poc.py excerpt: "def chunk_text(text: str, chunk_size: int = 400, overlap: int = 80)" and "def build_index(... chunk_size: int = 400, overlap: int = 80, batch_size: int = 16,)"; FILE generated_package\poc\config.yaml path rag.chunk_size_tokens = 400, rag.chunk_overlap_tokens = 80, models.embedding = "text-embedding-3-large"</t>
-  </si>
-  <si>
-    <t>Embedding deployment name is unconfirmed; Chroma vector store is an unconfirmed PoC assumption; chunking defaults are not fixed numerically and are expressed as defaults such as structure_aware/moderate.</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT: $.assumptions[0].text = "Embedding deployment name for Azure OpenAI is provided via environment variable AZURE_OPENAI_EMBEDDING_DEPLOYMENT. The specific model name is not user-confirmed."; $.assumptions[1].text = "RAGWorkflow uses a Chroma vector store (persist=True) for the PoC. The RBAC role filter is implemented as a Chroma metadata filter on the allowed_roles field, applied before similarity retrieval."; $.workflow.steps[1].parameters.chunking_strategy = "structure_aware"; $.workflow.steps[1].parameters.chunk_overlap = "moderate"; $.technical_spec.model_preferences.embedding_model = "${AZURE_OPENAI_EMBEDDING_DEPLOYMENT}"; $.models.embedding_model = "${AZURE_OPENAI_EMBEDDING_DEPLOYMENT}". PoC file corroboration: generated_package\poc\run_poc.py excerpt `workflow = RAGWorkflow(... persist=True, persist_path=str(chroma_dir), collection_name="manufacturing_knowledge", citations=True, conversation_history=False, stream=False, retriever_top_k=4 )`.</t>
+    <t>embedding deployment name treated as environment setting/assumption; Chroma/local vector store and retention/settings called out as assumptions or implementation choices; model temperature set to 1.0 in blueprint/config</t>
+  </si>
+  <si>
+    <t>GENERATED BLUEPRINT technical_spec.model_preferences.embedding_model = "Azure OpenAI embedding deployment supported by RAGWorkflow; exact deployment name is an environment setting"; GENERATED BLUEPRINT assumptions[1].text = "The exact Azure OpenAI embedding deployment name was not specified; the PoC will read it from an environment variable and default to a model compatible with RAGWorkflow (text-embedding-3-large)."; GENERATED BLUEPRINT components.selected_modules[0].reason = "... using a local persistent vector store (Chroma) ..."; GENERATED BLUEPRINT change_log[1].change = "... answer generation calls the underlying chat client directly ... to honor the user's explicit temperature=1.0 and reasoning_effort=medium ..."; FILE generated_package\poc\config.yaml models.temperature = 1.0; FILE generated_package\poc\run_poc.py: embedding_model = os.getenv("RAG_EMBEDDING_DEPLOYMENT") or config.get("models", {}).get("embedding") and VectorStore(... collection_name="gaik_rag_manufacturing_kb")</t>
+  </si>
+  <si>
+    <t>Embedding deployment name is an assumption/env setting; Chroma vector store and other implementation defaults are assumptions; chunking/overlap are set as implementation parameters in the blueprint.</t>
+  </si>
+  <si>
+    <t>Blueprint $.assumptions[0].text = "Embedding deployment name for Azure OpenAI is provided via environment variable AZURE_OPENAI_EMBEDDING_DEPLOYMENT. The specific model name is not user-confirmed." Blueprint $.assumptions[1].text = "RAGWorkflow uses a Chroma vector store (persist=True) for the PoC..." Blueprint $.workflow.steps[1].parameters.chunking_strategy = "structure_aware" and $.workflow.steps[1].parameters.chunk_overlap = "moderate". Conversation L0188-L0189: "Use an Azure OpenAI embedding model supported by the selected GAIK RAG workflow; the exact embedding deployment name is an environment setting... Valid implementation defaults may be recorded as assumptions, not user-confirmed requirements." Additional concrete PoC config value: generated_package\poc\config.yaml -&gt; $.models.temperature = 1.0.</t>
   </si>
   <si>
     <t>EQ2 Configuration</t>
@@ -1254,16 +1259,16 @@
     <t>GAIK registry; scenario oracle</t>
   </si>
   <si>
-    <t>knowledge_access; RAG-based assistant / role-aware question-answering assistant</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT: $.use_case.knowledge_processes = ["knowledge_access"]; $.business_spec.proposed_solution = "A RAG-based assistant that accepts natural-language questions, applies pre-retrieval RBAC based on the requestor role, retrieves semantically relevant chunks from allowed documents only, and generates cited answers in a structured RAGAnswerRecord format."</t>
-  </si>
-  <si>
-    <t>knowledge_access; RAG-based assistant / role-aware RAG assistant</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT use_case.knowledge_processes = ["knowledge_access"]; GENERATED BLUEPRINT use_case.description = "Role-aware RAG assistant that answers employee questions..."; GENERATED BLUEPRINT business_spec.proposed_solution = "RAG-based assistant..."</t>
+    <t>knowledge_access; classified as rag / employee knowledge retrieval</t>
+  </si>
+  <si>
+    <t>generated_blueprint: use_case.knowledge_processes[0] = "knowledge_access"; conversation L0324-L0326: "Knowledge process | knowledge_access" and "Description | Role-aware RAG assistant..."; conversation L0046-L0047: "Pattern: `rag` — document collection + question answering"</t>
+  </si>
+  <si>
+    <t>knowledge_access; RAG use case / employee knowledge retrieval</t>
+  </si>
+  <si>
+    <t>generated blueprint: use_case.knowledge_processes = ["knowledge_access"]; generated blueprint: use_case.description = "Role-aware RAG assistant..."; conversation L0325-L0326: "Knowledge process | knowledge_access" and role-aware RAG assistant description</t>
   </si>
   <si>
     <t>EQ2-C02</t>
@@ -1278,16 +1283,13 @@
     <t>GAIK registry</t>
   </si>
   <si>
-    <t>Custom components selected instead of RAG-Workflow: RBACPreFilter, LocalVectorIndexer, CitedRAGPipeline; selected_modules is empty</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT: $.components.selected_modules = []; $.components.custom_components = ["RBACPreFilter", "LocalVectorIndexer", "CitedRAGPipeline"]; $.assumptions[0].text = "A local in-memory vector store (numpy cosine similarity or equivalent) is used for the PoC instead of PostgreSQL+pgvector, as the user explicitly requested a local vector store. The standard RAGWorkflow module is not selected."; $.traceability[2].component = "CitedRAGPipeline"</t>
-  </si>
-  <si>
     <t>RAGWorkflow selected as primary module</t>
   </si>
   <si>
-    <t>GENERATED BLUEPRINT components.selected_modules[0].id = "rag_workflow"; GENERATED BLUEPRINT components.selected_modules[0].name = "RAGWorkflow"; GENERATED BLUEPRINT components.selected_modules[0].reason = "Use case is document Q&amp;A with citations... RAGWorkflow covers the full indexing (chunking, embedding, storage) and retrieval-augmented generation pipeline."</t>
+    <t>generated_blueprint: components.selected_modules[0].name = "RAGWorkflow"; generated_blueprint: components.selected_modules[0].reason = "Document collection to cited answer -- RAGWorkflow covers indexing, retrieval, and cited-answer generation end-to-end..."; conversation L0475-L0477: "RAGWorkflow | module | Covers indexing, embedding, retrieval, and answer generation end-to-end."</t>
+  </si>
+  <si>
+    <t>generated blueprint: components.selected_modules[0].name = "RAGWorkflow"; generated blueprint: components.selected_modules[0].reason = "RAGWorkflow covers the full indexing (chunking, embedding, storage) and retrieval-augmented generation pipeline."; conversation L0475-L0476 identifies RAGWorkflow as the module covering indexing, embedding, retrieval, and answer generation end-to-end</t>
   </si>
   <si>
     <t>EQ2-C03</t>
@@ -1302,16 +1304,16 @@
     <t>scripted_answers.json; GAIK registry</t>
   </si>
   <si>
-    <t>Parse PDFs and create structure-aware chunks with metadata fields file_name, page_number, classification, allowed_roles</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT: $.workflow.steps[1].name = "Parse PDFs, chunk with metadata, embed, build local vector index"; $.workflow.steps[1].parameters.chunking_strategy = "structure_aware"; $.workflow.steps[1].parameters.metadata_fields = ["file_name", "page_number", "classification", "allowed_roles"]; $.business_spec.input_artifacts = ["employee_travel_policy.pdf", "mx200_maintenance_manual.pdf", "project_aurora_pricing_strategy.pdf", "access_manifest.json", "query_set.json", "poc_input_bundle.json"]; PoC file generated_package\poc\run_poc.py: docstring step 2 = "ingest_and_index  — parse PDFs page-by-page, structure-aware chunk, embed, build local in-memory numpy vector index with full metadata"; parse_pdf_by_page docstring = "Returns [{text, page_number (1-based)}]"; build_index docstring = "Each chunk dict: text, file_name, page_number, classification, allowed_roles, embedding"</t>
-  </si>
-  <si>
-    <t>Index all three PDFs with structure-aware chunking and RBAC/citation metadata fields classification, allowed_roles, file_name, page_number</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT business_spec.input_artifacts = ["employee_travel_policy.pdf", "mx200_maintenance_manual.pdf", "project_aurora_pricing_strategy.pdf", ...]; GENERATED BLUEPRINT workflow.steps[1].parameters.chunking_strategy = "structure_aware"; GENERATED BLUEPRINT workflow.steps[1].parameters.rbac_metadata_fields = ["classification", "allowed_roles", "file_name", "page_number"]; GENERATED BLUEPRINT target_output_spec.validation_rules[2] = "Each citation must be a two-element list [string file_name, integer page_number] with 1-based page number"; PoC file generated_package\poc\run_poc.py excerpt: "workflow.index_documents(doc_paths, filenames=doc_filenames)" and build_citations() uses metadata keys "page_number" and document name to emit 1-based page numbers.</t>
+    <t>Parse the three PDFs and attach role metadata to chunks; metadata includes document_name and page_number, with role flags derived from access manifest</t>
+  </si>
+  <si>
+    <t>conversation L0156-L0156: "The evaluated collection contains three synthetic, text-based English PDFs... `employee_travel_policy.pdf`, `mx200_maintenance_manual.pdf`, and ... `project_aurora_pricing_strategy.pdf`."; generated_package\poc\run_poc.py excerpt: `for pdf_path in sorted(documents_dir.glob("*.pdf")):` and `chunks = parser.convert_doc_to_chunks_with_vision(str(pdf_path), document_name=filename)` and `chunk.metadata.update(flags)`; generated_package\poc\run_poc.py excerpt: `build_role_flags(...)` builds `{"role_employee": bool, "role_manager": bool}` from `access_manifest.json`; conversation L0156-L0156: "Each document has a title, filename, classification, allowed-role metadata, and 1-based PDF page-number metadata."</t>
+  </si>
+  <si>
+    <t>Index all three PDFs; structure_aware chunking; preserve classification, allowed_roles, file_name, page_number metadata</t>
+  </si>
+  <si>
+    <t>generated blueprint: business_spec.input_artifacts = ["employee_travel_policy.pdf", "mx200_maintenance_manual.pdf", "project_aurora_pricing_strategy.pdf", "access_manifest.json", "query_set.json", "poc_input_bundle.json"]; generated blueprint: workflow.steps[1].parameters.chunking_strategy = "structure_aware"; generated blueprint: workflow.steps[1].parameters.rbac_metadata_fields = ["classification", "allowed_roles", "file_name", "page_number"]; conversation L0156: "Each document has a title, filename, classification, allowed-role metadata, and 1-based PDF page-number metadata."</t>
   </si>
   <si>
     <t>EQ2-C04</t>
@@ -1323,16 +1325,16 @@
     <t>Create embeddings and index chunks in a vector store while preserving citation and access metadata.</t>
   </si>
   <si>
-    <t>Embed chunks and build a local vector index preserving chunk metadata including citation/access fields</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT: $.workflow.steps[1].name = "Parse PDFs, chunk with metadata, embed, build local vector index"; $.workflow.steps[1].parameters.embedding_model = "from_env_AZURE_EMBEDDING_DEPLOYMENT"; $.artifacts.local_vector_index.type = "vector_index"; $.artifacts.chunked_documents.type = "text_chunks"; PoC file generated_package\poc\run_poc.py: build_index docstring = "Parse all PDFs, chunk with access metadata, embed, return chunk list. Each chunk dict: text, file_name, page_number, classification, allowed_roles, embedding"</t>
-  </si>
-  <si>
-    <t>RAGWorkflow performs chunking, embedding, and storage/indexing with citation/access metadata preserved</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT components.selected_modules[0].reason = "RAGWorkflow covers the full indexing (chunking, embedding, storage) and retrieval-augmented generation pipeline."; GENERATED BLUEPRINT technical_spec.model_preferences.embedding_model = "${AZURE_OPENAI_EMBEDDING_DEPLOYMENT}"; GENERATED BLUEPRINT technical_spec.security_constraints = "...per-chunk allowed_roles metadata stored in the vector index."; GENERATED BLUEPRINT workflow.steps[1].parameters.rbac_metadata_fields = ["classification", "allowed_roles", "file_name", "page_number"]; PoC file generated_package\poc\run_poc.py excerpt: "workflow.index_documents(doc_paths, filenames=doc_filenames)"</t>
+    <t>Embed chunks and store them in a persistent vector store with metadata preserved</t>
+  </si>
+  <si>
+    <t>generated_package\poc\run_poc.py excerpt: `embeddings, docs = embedder.embed(all_chunks)` and `vector_store.add(docs, embeddings)`; generated_package\poc\run_poc.py excerpt: `vector_store = VectorStore(persist=True, persist_path=str(persist_path), collection_name="gaik_rag_manufacturing_kb")`; generated_blueprint: workflow.steps[3].parameters.persist = true; generated_blueprint: workflow.steps[3].parameters.persist_path = "poc/chroma_store"; generated_blueprint: workflow.steps[3].parameters.collection_name = "gaik_rag_manufacturing_kb"</t>
+  </si>
+  <si>
+    <t>RAGWorkflow covers embedding/storage with persisted collection</t>
+  </si>
+  <si>
+    <t>generated blueprint: components.selected_modules[0].reason = "RAGWorkflow covers the full indexing (chunking, embedding, storage) and retrieval-augmented generation pipeline."; generated blueprint: workflow.steps[1].component = "RAGWorkflow"; generated blueprint: workflow.steps[1].parameters.persist = true; generated blueprint: technical_spec.security_constraints = "Role-based access control enforced via per-chunk allowed_roles metadata stored in the vector index."</t>
   </si>
   <si>
     <t>EQ2-C05</t>
@@ -1344,16 +1346,16 @@
     <t>Apply allowed_roles metadata filtering before semantic retrieval; retrieve the top four eligible chunks.</t>
   </si>
   <si>
-    <t>Pre-retrieval RBAC with trusted role metadata; top_k = 4 eligible chunks</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT: $.workflow.steps[2].name = "Apply RBAC pre-filter and retrieve top-4 eligible chunks per query"; $.workflow.steps[2].parameters.role_source = "trusted_request_metadata"; $.workflow.steps[2].parameters.filter_timing = "pre_retrieval"; $.workflow.steps[2].parameters.top_k = 4; $.technical_spec.security_constraints[0] = "RBAC pre-filter: role from trusted request metadata (not inferred from question); access_manifest.json maps documents to allowed_roles; unauthorized chunks must never enter model context"; PoC file generated_package\poc\run_poc.py: rbac_check_and_retrieve docstring steps 4-5 = "Filter the chunk pool to role-permitted chunks only. Retrieve top-k by cosine similarity from the permitted pool." and function code `permitted_indices = [i for i, c in enumerate(all_chunks) if role in c["allowed_roles"]]` then `top_k_pos = np.argsort(permitted_sims)[-top_k:][::-1]`</t>
-  </si>
-  <si>
-    <t>Top-k = 4; role filter on allowed_roles intended before retrieval in blueprint, but PoC uses full-index check first then allowed-document filter</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.security_constraints = "Role filter applied before similarity retrieval so only chunks where allowed_roles contains the query role are candidates."; GENERATED BLUEPRINT workflow.steps[1].parameters.retriever_top_k = 4; GENERATED BLUEPRINT workflow.steps[1].parameters.role_filter_field = "allowed_roles"; GENERATED BLUEPRINT workflow.steps[1].parameters.role_source = "query_metadata"; PoC file generated_package\poc\run_poc.py docstring excerpt: "2. Query the FULL index (no filter)... 3. Otherwise query with a Chroma `document_name` filter..."; PoC file generated_package\poc\run_poc.py excerpt in process_query(): "full_result = workflow.ask(question, top_k=top_k, stream=False)" then "role_result = workflow.ask(question, top_k=top_k, filters=filters, stream=False)" and main() calls process_query(... top_k=4)</t>
+    <t>Pre-retrieval RBAC filter using role metadata; top_k = 4</t>
+  </si>
+  <si>
+    <t>generated_blueprint: workflow.steps[3].parameters.retriever_top_k = 4; generated_blueprint: workflow.steps[3].parameters.access_control = "Pre-retrieval RBAC: each indexed chunk is tagged with boolean role_&lt;role&gt; metadata flags... ask() is called with filters={'role_&lt;requesting_role&gt;': true} so unauthorized chunks are excluded from the similarity search itself..."; generated_package\poc\run_poc.py excerpt: `authorized_chunks = retriever.search(question, top_k=4, filters={role_key: True}, include_scores=True)`; conversation L0078-L0078: "Access filtering must happen before retrieval so unauthorized chunks never enter the model context."</t>
+  </si>
+  <si>
+    <t>Role filter before retrieval; retriever_top_k = 4</t>
+  </si>
+  <si>
+    <t>generated blueprint: technical_spec.security_constraints = "Role filter applied before similarity retrieval so only chunks where allowed_roles contains the query role are candidates."; generated blueprint: workflow.steps[1].parameters.role_filter_field = "allowed_roles"; generated blueprint: workflow.steps[1].parameters.role_source = "query_metadata"; generated blueprint: workflow.steps[1].parameters.retriever_top_k = 4; conversation L0078: "Access filtering must happen before retrieval so unauthorized chunks never enter the model context."</t>
   </si>
   <si>
     <t>EQ2-C06</t>
@@ -1365,16 +1367,16 @@
     <t>AnswerGenerator or equivalent is instructed to use only retrieved context, cite sources, abstain without support, and refuse denied access without leakage.</t>
   </si>
   <si>
-    <t>Grounding policy retrieved_content_only; cite [file_name, page_number]; no support =&gt; not found/do not speculate; denied returns refusal without restricted facts</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT: $.workflow.steps[3].parameters.grounding_policy = "retrieved_content_only"; $.workflow.steps[3].parameters.no_support_policy = "state_not_found_do_not_speculate"; $.workflow.steps[3].parameters.citation_format = "[file_name, page_number]"; $.target_output_spec.field_descriptions.refusal_reason = "Required (non-null) when access_decision=denied; must not reveal restricted facts; null otherwise"; $.target_output_spec.validation_rules = ["citations must be an empty list when access_decision=denied", "refusal_reason must be non-null when access_decision=denied", "answer must not reveal restricted content when access_decision=denied", "allowed factual answers must include at least one citation to a document permitted for that role"]; PoC file generated_package\poc\run_poc.py: _SYSTEM_PROMPT includes "using ONLY the document passages provided", "Every factual claim must be cited as [filename, page_number]", and "If the passages do not contain enough information, respond: 'The information was not found in the available documents.' Do not speculate"; denied_record answer = "Access denied. You are not authorised to access this information."</t>
-  </si>
-  <si>
-    <t>No-speculation grounding with citations, denial without leakage, and no answer from model memory when evidence absent</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT workflow.steps[1].parameters.citations = true; GENERATED BLUEPRINT workflow.steps[1].parameters.no_speculation = true; GENERATED BLUEPRINT technical_spec.security_constraints = "Management-confidential documents ... are never retrieved or disclosed to users with the 'employee' role."; GENERATED BLUEPRINT target_output_spec.validation_rules = ["access_decision must be 'allowed' or 'denied'", "Allowed factual answers require at least one citation", "Each citation must be a two-element list [string file_name, integer page_number] with 1-based page number", "Denied answers require refusal_reason, empty citations list, and must not reveal restricted content", "Do not answer from model memory when authorized evidence is absent"]; PoC file generated_package\poc\run_poc.py excerpt denied answer: "Access denied. The information you requested is contained in a document that your role is not authorised to access." and refusal_reason: "The requested information exists in a management-confidential document..."</t>
+    <t>Answer only from provided context; no outside knowledge or guessing; say not found if unsupported; denied answers return restricted-message with no citations</t>
+  </si>
+  <si>
+    <t>generated_package\poc\run_poc.py excerpt from `ANSWER_PROMPT`: "Answer the question using ONLY the information in the context below. Do not use any outside knowledge and do not guess." and "If the context does not contain enough information to answer, say plainly that the information was not found in the documents you have access to." and "Do not invent bracketed citations yourself -- citations are attached separately by the pipeline."; generated_package\poc\run_poc.py excerpt from denied branch: `access_decision="denied"`, `answer="I'm not able to share that information -- it is restricted to a different role."`, `citations=[]`; generated_blueprint: technical_spec.security_constraints = "Denied answers must not reveal restricted facts or citations."</t>
+  </si>
+  <si>
+    <t>No speculation; citations required; deny when no allowed chunks; denied answers must not reveal restricted content</t>
+  </si>
+  <si>
+    <t>generated blueprint: workflow.steps[1].parameters.no_speculation = true; generated blueprint: workflow.steps[1].parameters.citations = true; generated blueprint: workflow.steps[1].parameters.deny_when_no_allowed_chunks = true; generated blueprint: target_output_spec.validation_rules[3] = "Denied answers require refusal_reason, empty citations list, and must not reveal restricted content"; generated blueprint: target_output_spec.validation_rules[4] = "Do not answer from model memory when authorized evidence is absent"</t>
   </si>
   <si>
     <t>EQ2-C07</t>
@@ -1386,16 +1388,16 @@
     <t>Ingest and index documents, receive query and role, filter eligible documents, retrieve evidence, generate answer, validate citations and access behavior, then return result.</t>
   </si>
   <si>
-    <t>Workflow sequence: load input bundle -&gt; ingest/index -&gt; apply RBAC and retrieve -&gt; generate answers; validation rules defined separately</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT: $.workflow.steps[0].id = "load_input"; $.workflow.steps[1].id = "ingest_and_index" depends_on ["load_input"]; $.workflow.steps[2].id = "apply_rbac_and_retrieve" depends_on ["ingest_and_index"]; $.workflow.steps[3].id = "generate_answers" depends_on ["apply_rbac_and_retrieve"]; $.target_output_spec.validation_rules = ["access_decision must be 'allowed' or 'denied'", "citations must be an empty list when access_decision=denied", "refusal_reason must be non-null when access_decision=denied", "each citation must be exactly [str, int] (filename, 1-based page number)", "answer must not reveal restricted content when access_decision=denied", "allowed factual answers must include at least one citation to a document permitted for that role", "exact values must be preserved: EUR 180, 250 operating hours, 1,000 operating hours, 1.8 bar, 12 percent, 22 percent"]; PoC file generated_package\poc\run_poc.py docstring pipeline lists steps 1-4 in the same order</t>
-  </si>
-  <si>
-    <t>Load bundle, index documents, process queries with role-filtered retrieval, then save results; validation appears in evaluation/validation sections rather than as explicit workflow steps</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT workflow.steps[0].name = "Load PoC input bundle"; GENERATED BLUEPRINT workflow.steps[1].name = "Index documents and process queries with role-filtered retrieval"; GENERATED BLUEPRINT workflow.steps[2].name = "Save RAGAnswerRecord results to output file"; GENERATED BLUEPRINT workflow.steps[1].parameters = {"retriever_top_k": 4, "role_filter_field": "allowed_roles", "deny_when_no_allowed_chunks": true, "citation_format": "[file_name, page_number]", ...}; GENERATED BLUEPRINT validation = {"human_review_required": false, "completeness_check": true, "hallucination_check": false}; GENERATED BLUEPRINT evaluation.metrics = ["access_control_correctness", "citation_accuracy", "answer_groundedness", "refusal_correctness"]</t>
+    <t>Provide bundle/documents + access manifest + queries, then generate role-aware answers by indexing with role metadata, retrieving role-filtered context, and generating cited answers</t>
+  </si>
+  <si>
+    <t>generated_blueprint: workflow.steps[0].id = "upload_documents"; workflow.steps[1].id = "provide_access_manifest"; workflow.steps[2].id = "submit_queries"; workflow.steps[3].id = "generate_role_aware_answers"; workflow.steps[3].name = "Index documents with role metadata, retrieve role-filtered context, generate cited answer per query"; generated_package\poc\run_poc.py main flow excerpt: `load_bundle(...)`, `build_role_flags(access_manifest)`, `index_documents(...)`, loop over `queries`, then `classify_and_answer(...)`, then write JSON to output file</t>
+  </si>
+  <si>
+    <t>Load bundle -&gt; run role-filtered RAG pipeline -&gt; save results</t>
+  </si>
+  <si>
+    <t>generated blueprint: workflow.steps[0].id = "load_input_bundle"; generated blueprint: workflow.steps[1].id = "run_rag_pipeline" with name "Index documents and process queries with role-filtered retrieval"; generated blueprint: workflow.steps[2].id = "save_results"; Mermaid workflow in conversation L0553-L0559 shows order: provide_bundle -&gt; apply_rbac_filter -&gt; index_and_query -&gt; format_results</t>
   </si>
   <si>
     <t>EQ2-C08</t>
@@ -1407,16 +1409,16 @@
     <t>Each result includes query_id, role, question, access_decision, answer, citations as [file_name, page_number] pairs, and conditional refusal_reason in JSON.</t>
   </si>
   <si>
-    <t>RAGAnswerRecord fields: query_id, role, question, access_decision, answer, citations, refusal_reason; citations are [file_name, page_number]; refusal_reason conditional</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT: $.target_output_spec.schema_name = "RAGAnswerRecord"; $.target_output_spec.fields = ["query_id", "role", "question", "access_decision", "answer", "citations", "refusal_reason"]; $.target_output_spec.field_descriptions.citations = "List of [file_name, page_number] pairs (1-based integer); empty list when access_decision=denied"; $.target_output_spec.field_descriptions.refusal_reason = "Required (non-null) when access_decision=denied; must not reveal restricted facts; null otherwise"; PoC file generated_package\poc\prompts\extraction_requirements.md lines 1-7 enumerate the same fields and constraints</t>
-  </si>
-  <si>
-    <t>Output JSON records with query_id, role, question, access_decision, answer, citations [file_name, page_number], and optional refusal_reason when denied</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT target_output_spec.schema_name = "RAGAnswerRecord"; GENERATED BLUEPRINT target_output_spec.fields = ["query_id", "role", "question", "access_decision", "answer", "citations", "refusal_reason"]; GENERATED BLUEPRINT target_output_spec.field_descriptions.citations = "List of [file_name, page_number] pairs citing source material. Empty list for denied queries."; GENERATED BLUEPRINT target_output_spec.field_descriptions.refusal_reason = "Required when access_decision is 'denied'..."; PoC file generated_package\poc\run_poc.py excerpt returns dicts with keys "query_id", "role", "question", "access_decision", "answer", "citations", "refusal_reason" and saves via "json.dumps(results, indent=2, ensure_ascii=False)"</t>
+    <t>Output schema fields: query_id, role, question, access_decision, answer, citations, optional refusal_reason</t>
+  </si>
+  <si>
+    <t>generated_blueprint: target_output_spec.fields = ["query_id", "role", "question", "access_decision", "answer", "citations", "refusal_reason"]; generated_blueprint: target_output_spec.field_types.citations = "list of [file_name: str, page_number: int (1-based)]"; generated_blueprint: target_output_spec.optional_fields[0] = "refusal_reason"; generated_blueprint: target_output_spec.allowed_values.access_decision = ["allowed", "denied"]</t>
+  </si>
+  <si>
+    <t>Output fields: query_id, role, question, access_decision, answer, citations, refusal_reason</t>
+  </si>
+  <si>
+    <t>generated blueprint: target_output_spec.fields = ["query_id", "role", "question", "access_decision", "answer", "citations", "refusal_reason"]; generated blueprint: target_output_spec.field_descriptions.citations = "List of [file_name, page_number] pairs..."; generated blueprint: target_output_spec.field_descriptions.refusal_reason = "Required when access_decision is 'denied'..."</t>
   </si>
   <si>
     <t>EQ2-C09</t>
@@ -1428,16 +1430,16 @@
     <t>CLI accepts poc_input_bundle.json through --input, resolves the supplied local documents, access manifest, and four-query set, and saves JSON; web UI, live repository, and enterprise identity are not required.</t>
   </si>
   <si>
-    <t>CLI PoC via --input poc_input_bundle.json; resolves local docs/access manifest/query set relative to bundle; saves output/results.json; enterprise identity out of scope; web UI/live repository NOT FOUND</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT: $.technical_spec.runtime_interface = "cli"; $.technical_spec.runtime_entrypoint = "python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;"; $.business_spec.poc_goal = "Demonstrate role-aware, citation-grounded question answering over three PDF documents using a local vector store and trusted role metadata. CLI: python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;. Execute all four role-tagged queries (Q01-Q04) and save non-empty parseable JSON results to output/results.json."; $.workflow.steps[0].parameters.cli_arg = "--input &lt;path-to-poc_input_bundle.json&gt;"; $.workflow.steps[0].parameters.path_resolution = "all other files resolved relative to poc_input_bundle.json"; $.technical_spec.security_constraints[3] = "No audit-log service required for PoC; enterprise identity integration is out of PoC scope"; PoC file generated_package\poc\run_poc.py docstring Usage = "python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;" and Output = "output/results.json"; load_bundle docstring = "All file references are resolved relative to bundle_path's parent directory."; searched for explicit wizard evidence of 'web UI not required' and 'live repository not required' in GENERATED BLUEPRINT and provided PoC files: NOT FOUND</t>
-  </si>
-  <si>
-    <t>CLI PoC takes --input poc_input_bundle.json, resolves local docs/manifest/query set, and saves JSON results; no web UI, live repository, or enterprise identity targets listed</t>
-  </si>
-  <si>
-    <t>GENERATED BLUEPRINT technical_spec.runtime_interface = "cli"; GENERATED BLUEPRINT runtime.interface = "cli"; GENERATED BLUEPRINT runtime.entrypoint = "poc/run_poc.py"; GENERATED BLUEPRINT workflow.steps[0].parameters.entrypoint_flag = "--input"; GENERATED BLUEPRINT workflow.steps[0].parameters.description = "User provides path to poc_input_bundle.json via CLI. All referenced files (PDFs, access_manifest.json, query_set.json) are resolved relative to the bundle file."; GENERATED BLUEPRINT technical_spec.integration_targets = []; PoC file generated_package\poc\run_poc.py usage excerpt: "python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;"; PoC file generated_package\poc\run_poc.py resolves bundle fields: "manifest_path = (bundle_dir / bundle['access_manifest']).resolve()", "query_set_path = (bundle_dir / bundle['query_set']).resolve()", "docs_dir = (bundle_dir / bundle['documents_directory']).resolve()"; PoC file generated_package\poc\run_poc.py saves output to "output/results.json"</t>
+    <t>CLI `python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;`; resolves local bundle-relative files; executes four role-tagged queries; web UI/live repository/enterprise sign-in out of scope</t>
+  </si>
+  <si>
+    <t>generated_blueprint: technical_spec.runtime_interface = "CLI: `python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;`, resolving access_manifest.json, query_set.json, and the documents directory relative to that bundle file."; generated_package\poc\run_poc.py docstring: `Usage: python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;` and `The bundle file points ... to: - documents_directory ... - access_manifest ... - query_set`; generated_package\poc\run_poc.py excerpt: `parser.add_argument("--input", required=True, help="Path to poc_input_bundle.json ...")`; conversation L0188-L0190: "It must support the command `python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;`, resolve the other supplied files relative to that bundle, execute all four role-tagged queries... A web interface, live repository connector, enterprise sign-in... are outside the first PoC."</t>
+  </si>
+  <si>
+    <t>CLI run_poc.py --input &lt;poc_input_bundle.json&gt;; resolve local files relative to bundle; execute four queries; web UI/live repo/enterprise sign-in out of scope</t>
+  </si>
+  <si>
+    <t>generated blueprint: technical_spec.runtime_interface = "cli"; generated blueprint: workflow.steps[0].parameters.entrypoint_flag = "--input"; generated blueprint: workflow.steps[0].parameters.description = "User provides path to poc_input_bundle.json via CLI. All referenced files (PDFs, access_manifest.json, query_set.json) are resolved relative to the bundle file."; conversation L0188-L0190 specifies command `python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;`, local bundle files, four role-tagged queries, and that web interface/live repository connector/enterprise sign-in are outside scope; PoC file generated_package\poc\run_poc.py lines in docstring: "Usage: python run_poc.py --input &lt;path-to-poc_input_bundle.json&gt;" and code resolves bundle["access_manifest"], bundle["query_set"], bundle["documents_directory"] relative to bundle_path.parent</t>
   </si>
   <si>
     <t>EQ3 Package</t>
@@ -1458,10 +1460,10 @@
     <t>generated package</t>
   </si>
   <si>
-    <t>Blueprint parsed; 21672 bytes.</t>
-  </si>
-  <si>
-    <t>C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_01\generated_package\use_case.blueprint.json: JSON parsed successfully.</t>
+    <t>Blueprint parsed; 23067 bytes.</t>
+  </si>
+  <si>
+    <t>C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_01\generated_package\use_case.blueprint.json: JSON parsed successfully.</t>
   </si>
   <si>
     <t>pass</t>
@@ -1470,7 +1472,7 @@
     <t>Blueprint parsed; 21406 bytes.</t>
   </si>
   <si>
-    <t>C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_02\generated_package\use_case.blueprint.json: JSON parsed successfully.</t>
+    <t>C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_02\generated_package\use_case.blueprint.json: JSON parsed successfully.</t>
   </si>
   <si>
     <t>EQ3-P02</t>
@@ -1485,21 +1487,6 @@
     <t>validator command; exit code; validator output excerpt</t>
   </si>
   <si>
-    <t>Validator exit code 0.</t>
-  </si>
-  <si>
-    <t>Resolution: auto-discovered at C:\Users\h02317\gaik-toolkit\implementation_layer\solution_wizard\scripts\validate_blueprint.py; command: ['C:\\Users\\h02317\\AppData\\Local\\Programs\\Python\\Python312\\python.exe', 'C:\\Users\\h02317\\gaik-toolkit\\implementation_layer\\solution_wizard\\scripts\\validate_blueprint.py', '--blueprint', 'C:\\Users\\h02317\\Downloads\\Wizard evaluation\\UC03_document_rag_evaluation\\runs\\run_01\\generated_package\\use_case.blueprint.json']; cwd: C:\Users\h02317\gaik-toolkit\implementation_layer\solution_wizard; output: Validation PASSED
-  WARNING Rule 11: High-impact assumption 'assumption_002' is still unconfirmed. Resolve before production packaging. Text: "The knowledge_owner role is treated as having the same document access as manager (all three documents). The user specified employee and manager access tiers; knowledge_owner was described functionally but not mapped to an access tier."
-  WARNING Rule 11: High-impact assumption 'assumption_003' is still unconfirmed. Resolve before production packaging. Text: "Structure-aware chunking uses paragraph or section boundaries with moderate overlap (approximately 10-20% of chunk size). Exact chunk size defaults to approximately 512 tokens."
-  WARNING Rule 11: High-impact assumption 'assumption_004' is still unconfirmed. Resolve before production packaging. Text: "The Azure OpenAI embedding deployment name is provided via environment variable AZURE_EMBEDDING_DEPLOYMENT. The specific model name is not user-confirmed."</t>
-  </si>
-  <si>
-    <t>Resolution: auto-discovered at C:\Users\h02317\gaik-toolkit\implementation_layer\solution_wizard\scripts\validate_blueprint.py; command: ['C:\\Users\\h02317\\AppData\\Local\\Programs\\Python\\Python312\\python.exe', 'C:\\Users\\h02317\\gaik-toolkit\\implementation_layer\\solution_wizard\\scripts\\validate_blueprint.py', '--blueprint', 'C:\\Users\\h02317\\Downloads\\Wizard evaluation\\UC03_document_rag_evaluation\\runs\\run_02\\generated_package\\use_case.blueprint.json']; cwd: C:\Users\h02317\gaik-toolkit\implementation_layer\solution_wizard; output: Validation PASSED
-  WARNING Rule 11: High-impact assumption 'assumption_001' is still unconfirmed. Resolve before production packaging. Text: "Embedding deployment name for Azure OpenAI is provided via environment variable AZURE_OPENAI_EMBEDDING_DEPLOYMENT. The specific model name is not user-confirmed."
-  WARNING Rule 11: High-impact assumption 'assumption_002' is still unconfirmed. Resolve before production packaging. Text: "RAGWorkflow uses a Chroma vector store (persist=True) for the PoC. The RBAC role filter is implemented as a Chroma metadata filter on the allowed_roles field, applied before similarity retrieval."
-  WARNING Rule 11: High-impact assumption 'assumption_005' is still unconfirmed. Resolve before production packaging. Text: "The documents are assumed not to contain personal data. The management-confidential document is commercially sensitive but not personal data. This affects governance.data_handling.contains_personal_data."</t>
-  </si>
-  <si>
     <t>EQ3-P03</t>
   </si>
   <si>
@@ -1515,7 +1502,7 @@
     <t>Artifact flow is internally consistent.</t>
   </si>
   <si>
-    <t>Checked 4 workflow steps and 8 artifacts. Undeclared references: none; invalid dependencies: none; producer mismatches: none.</t>
+    <t>Checked 4 workflow steps and 4 artifacts. Undeclared references: none; invalid dependencies: none; producer mismatches: none.</t>
   </si>
   <si>
     <t>Checked 3 workflow steps and 6 artifacts. Undeclared references: none; invalid dependencies: none; producer mismatches: none.</t>
@@ -1536,10 +1523,10 @@
     <t>Mermaid workflow present and covers steps.</t>
   </si>
   <si>
-    <t>C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_01\generated_package\workflow.mmd; 637 bytes; matched 4/4 steps: ['load_input', 'ingest_and_index', 'apply_rbac_and_retrieve', 'generate_answers'].</t>
-  </si>
-  <si>
-    <t>C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_02\generated_package\workflow.mmd; 420 bytes; matched 3/3 steps: ['load_input_bundle', 'run_rag_pipeline', 'save_results'].</t>
+    <t>C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_01\generated_package\workflow.mmd; 721 bytes; matched 4/4 steps: ['upload_documents', 'provide_access_manifest', 'submit_queries', 'generate_role_aware_answers'].</t>
+  </si>
+  <si>
+    <t>C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_02\generated_package\workflow.mmd; 420 bytes; matched 3/3 steps: ['load_input_bundle', 'run_rag_pipeline', 'save_results'].</t>
   </si>
   <si>
     <t>EQ3-P05</t>
@@ -1557,10 +1544,10 @@
     <t>BPMN parsed and maps workflow steps.</t>
   </si>
   <si>
-    <t>C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_01\generated_package\workflow.bpmn; XML parsed; 97 element ids; matched 4/4 blueprint steps through BPMN ids/names/mapping.</t>
-  </si>
-  <si>
-    <t>C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_02\generated_package\workflow.bpmn; XML parsed; 75 element ids; matched 3/3 blueprint steps through BPMN ids/names/mapping.</t>
+    <t>C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_01\generated_package\workflow.bpmn; XML parsed; 84 element ids; matched 4/4 blueprint steps through BPMN ids/names/mapping.</t>
+  </si>
+  <si>
+    <t>C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_02\generated_package\workflow.bpmn; XML parsed; 75 element ids; matched 3/3 blueprint steps through BPMN ids/names/mapping.</t>
   </si>
   <si>
     <t>EQ3-P06</t>
@@ -1575,19 +1562,13 @@
     <t>generated package/poc</t>
   </si>
   <si>
-    <t>PoC scaffold contains all required file categories.</t>
-  </si>
-  <si>
-    <t>C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_01\generated_package\poc; matched files by category: {"entrypoint": ["run_poc.py"], "dependencies": ["requirements.txt"], "configuration": ["config.yaml"], "prompts": ["prompts\\extraction_requirements.md"], "schemas": ["schemas\\output_schema.json", "schemas\\output_schema.py", "schemas\\output_schema_requirements.json"]}</t>
-  </si>
-  <si>
     <t>PoC scaffold is missing one or more file categories.</t>
   </si>
   <si>
-    <t>C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_02\generated_package\poc; matched files by category: {"entrypoint": ["run_poc.py"], "dependencies": ["requirements.txt"], "configuration": ["config.yaml"], "prompts": [], "schemas": []}</t>
-  </si>
-  <si>
-    <t>fail</t>
+    <t>C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_01\generated_package\poc; matched files by category: {"entrypoint": ["run_poc.py"], "dependencies": ["requirements.txt"], "configuration": ["config.yaml", ".env.example"], "prompts": [], "schemas": ["schemas\\output_schema.py"]}</t>
+  </si>
+  <si>
+    <t>C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_02\generated_package\poc; matched files by category: {"entrypoint": ["run_poc.py"], "dependencies": ["requirements.txt"], "configuration": ["config.yaml", ".env.example"], "prompts": [], "schemas": []}</t>
   </si>
   <si>
     <t>EQ3-P07</t>
@@ -1605,7 +1586,7 @@
     <t>Documentation and PoC usage instructions are present.</t>
   </si>
   <si>
-    <t>Non-empty documents: ['docs\\developer_guide.md (5844 bytes)', 'docs\\evaluation_plan.md (5900 bytes)', 'docs\\genai_product_canvas.md (4674 bytes)', 'docs\\technical_specification.md (5933 bytes)', 'docs\\user_guide.md (2909 bytes)', 'poc\\README.md (3600 bytes)'].</t>
+    <t>Non-empty documents: ['docs\\developer_guide.md (7713 bytes)', 'docs\\evaluation_plan.md (5395 bytes)', 'docs\\genai_product_canvas.md (4315 bytes)', 'docs\\technical_specification.md (7525 bytes)', 'docs\\user_guide.md (3775 bytes)', 'poc\\README.md (4109 bytes)'].</t>
   </si>
   <si>
     <t>Non-empty documents: ['docs\\developer_guide.md (6735 bytes)', 'docs\\evaluation_plan.md (5564 bytes)', 'docs\\genai_product_canvas.md (4558 bytes)', 'docs\\technical_specification.md (5662 bytes)', 'docs\\user_guide.md (3597 bytes)', 'poc\\README.md (4368 bytes)'].</t>
@@ -1623,15 +1604,12 @@
     <t>blueprint traceability; selected components</t>
   </si>
   <si>
-    <t>Traceability is missing or does not mention selected assets.</t>
-  </si>
-  <si>
-    <t>Traceability entries=3; selected assets=[]; mentioned assets=[].</t>
-  </si>
-  <si>
     <t>Traceability entries connect selected GAIK assets to requirements.</t>
   </si>
   <si>
+    <t>Traceability entries=3; selected assets=['RAGWorkflow']; mentioned assets=['RAGWorkflow'].</t>
+  </si>
+  <si>
     <t>Traceability entries=2; selected assets=['RAGWorkflow']; mentioned assets=['RAGWorkflow'].</t>
   </si>
   <si>
@@ -1656,17 +1634,17 @@
     <t>setup exit code=0</t>
   </si>
   <si>
-    <t xml:space="preserve">C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_01\poc_execution.json; command=['C:\\Users\\h02317\\AppData\\Local\\Programs\\Python\\Python312\\python.exe', '-m', 'pip', 'install', '-r', 'requirements.txt']; stdout=Requirement already satisfied: pydantic&gt;=2 in c:\users\h02317\appdata\local\programs\python\python312\lib\site-packages (from -r requirements.txt (line 1)) (2.12.5)
+    <t xml:space="preserve">C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_01\poc_execution.json; command=['C:\\Users\\h02317\\AppData\\Local\\Programs\\Python\\Python312\\python.exe', '-m', 'pip', 'install', '-r', 'requirements.txt']; stdout=Requirement already satisfied: pydantic&gt;=2 in c:\users\h02317\appdata\local\programs\python\python312\lib\site-packages (from -r requirements.txt (line 1)) (2.12.5)
 Requirement already satisfied: python-dotenv in c:\users\h02317\appdata\local\programs\python\python312\lib\site-packages (from -r requirements.txt (line 2)) (1.2.1)
-Requirement already satisfied: pyyaml in c:\users\h02317\appdata\local\programs\python\python312\lib\site-packages (from -r requirements.txt (line 3)) (6.0.3)
-Requirement already satisfied: openai&gt;=1.30 in c:\users\h02317\appdata\local\programs\python\python312\lib\site-packages (from -r requirements.txt (line 4)) (2.8.1)
-Requirement already satisfied: numpy&gt;=1.26 in c:\users\h02317\appdata\local\programs\python\python312\lib\site-packages (from -r requirements.txt; stderr=
+Requirement already satisfied: pyyaml in c:\users\h02317\appdata\local\programs\python\python312\lib\site-packages (from -r requirements.txt (line 4)) (6.0.3)
+Requirement already satisfied: gaik[rag-workflow] in c:\users\h02317\appdata\local\programs\python\python312\lib\site-packages (from -r requirements.txt (line 3)) (0.5.18)
+Requirement already satisfied: annotated-types&gt;=0.6.0 in c:\users\h02317\appdata\local\programs\python\python312\lib\site-packages (from p; stderr=
 [notice] A new release of pip is available: 25.0.1 -&gt; 26.2.1
 [notice] To update, run: python.exe -m pip install --upgrade pip
 </t>
   </si>
   <si>
-    <t xml:space="preserve">C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_02\poc_execution.json; command=['C:\\Users\\h02317\\AppData\\Local\\Programs\\Python\\Python312\\python.exe', '-m', 'pip', 'install', '-r', 'requirements.txt']; stdout=Requirement already satisfied: pydantic&gt;=2 in c:\users\h02317\appdata\local\programs\python\python312\lib\site-packages (from -r requirements.txt (line 1)) (2.12.5)
+    <t xml:space="preserve">C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_02\poc_execution.json; command=['C:\\Users\\h02317\\AppData\\Local\\Programs\\Python\\Python312\\python.exe', '-m', 'pip', 'install', '-r', 'requirements.txt']; stdout=Requirement already satisfied: pydantic&gt;=2 in c:\users\h02317\appdata\local\programs\python\python312\lib\site-packages (from -r requirements.txt (line 1)) (2.12.5)
 Requirement already satisfied: python-dotenv in c:\users\h02317\appdata\local\programs\python\python312\lib\site-packages (from -r requirements.txt (line 2)) (1.2.1)
 Requirement already satisfied: pyyaml in c:\users\h02317\appdata\local\programs\python\python312\lib\site-packages (from -r requirements.txt (line 4)) (6.0.3)
 Requirement already satisfied: gaik[rag-workflow] in c:\users\h02317\appdata\local\programs\python\python312\lib\site-packages (from -r requirements.txt (line 3)) (0.5.16)
@@ -1688,25 +1666,30 @@
     <t>poc_execution.json; fixtures/rag_test_bundle.json</t>
   </si>
   <si>
-    <t>run exit code=1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_01\poc_execution.json; fixture={'path': 'C:\\Users\\h02317\\Downloads\\Wizard evaluation\\UC03_document_rag_evaluation\\fixtures\\poc_input_bundle.json', 'sha256': '0f39c932d5146754a0462ce9d09151c2238b8f980256ab7a201335970bc8da7e', 'size_bytes': 275}; command=['C:\\Users\\h02317\\AppData\\Local\\Programs\\Python\\Python312\\python.exe', 'run_poc.py', '--input', 'C:\\Users\\h02317\\Downloads\\Wizard evaluation\\UC03_document_rag_evaluation\\fixtures\\poc_input_bundle.json']; stdout==== Manufacturing Knowledge Base RAG Assistant — PoC ===
-Input bundle : C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\fixtures\poc_input_bundle.json
-Chat model   : gpt-5.4  (temp=0.0, reasoning=medium)
-Embedding    : text-embedding-3-large
-Top-k        : 4
-Documents found : []
-Access manifest : []
-Queries loaded  : 0
-; stderr=ERROR: No PDF files resolved from bundle.
-</t>
-  </si>
-  <si>
     <t>run exit code=0</t>
   </si>
   <si>
-    <t>C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_02\poc_execution.json; fixture={'path': 'C:\\Users\\h02317\\Downloads\\Wizard evaluation\\UC03_document_rag_evaluation\\fixtures\\poc_input_bundle.json', 'sha256': '0f39c932d5146754a0462ce9d09151c2238b8f980256ab7a201335970bc8da7e', 'size_bytes': 275}; command=['C:\\Users\\h02317\\AppData\\Local\\Programs\\Python\\Python312\\python.exe', 'run_poc.py', '--input', 'C:\\Users\\h02317\\Downloads\\Wizard evaluation\\UC03_document_rag_evaluation\\fixtures\\poc_input_bundle.json']; stdout=Warning: Additional format options not available. Only PDF will be supported.
+    <t>C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_01\poc_execution.json; fixture={'path': 'C:\\Users\\h02317\\Solution wizard evaluation\\use cases\\UC03_document_rag_evaluation\\fixtures\\poc_input_bundle.json', 'sha256': '0f39c932d5146754a0462ce9d09151c2238b8f980256ab7a201335970bc8da7e', 'size_bytes': 275}; command=['C:\\Users\\h02317\\AppData\\Local\\Programs\\Python\\Python312\\python.exe', 'run_poc.py', '--input', 'C:\\Users\\h02317\\Solution wizard evaluation\\use cases\\UC03_document_rag_evaluation\\fixtures\\poc_input_bundle.json']; stdout=Warning: Additional format options not available. Only PDF will be supported.
+Setting up RAG components...
+[Torch] version: 2.9.1+cu128, cuda available: True
+Using CUDA device: NVIDIA RTX PRO 2000 Blackwell Generation Laptop GPU (devices: 1)
+Indexing documents from C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\fixtures\poc_input\documents ...
+Processing PDF with vision enhancement: C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\fixtures\poc_input\documents\employee_travel_policy.pdf
+Document parsing complete. Pages: 5
+Found 0 images to analyze
+Chunk 1: document='employee_travel_policy.pdf', page=1, heading='Employee Travel Policy'
+Chunk 2: document='employee_travel_policy.pdf', page=1, heading='Classification: Internal ; stderr=INFO:chromadb.telemetry.product.posthog:Anonymized telemetry enabled. See                     https://docs.trychroma.com/telemetry for more information.
+INFO:docling.datamodel.document:detected formats: [&lt;InputFormat.PDF: 'pdf'&gt;]
+INFO:docling.document_converter:Going to convert document batch...
+INFO:docling.document_converter:Initializing pipeline for StandardPdfPipeline with options hash 9d7080cb3eda9f2b898afe6c94bebb46
+INFO:docling.models.factories.base_factory:Loading plugin 'docling_defaults'
+INFO:docling.models.factories:Registered picture descriptions: ['vlm', 'api']
+INFO:docling.models.factories.base_factory:Loading plugin 'docling_defaults'
+INFO:docling.models.factories:Registered ocr engines: ['auto', 'easyocr', 'ocrmac', 'rapidocr', 'tesserocr', 'tesseract']
+INFO:docling.models.</t>
+  </si>
+  <si>
+    <t>C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_02\poc_execution.json; fixture={'path': 'C:\\Users\\h02317\\Downloads\\Wizard evaluation\\UC03_document_rag_evaluation\\fixtures\\poc_input_bundle.json', 'sha256': '0f39c932d5146754a0462ce9d09151c2238b8f980256ab7a201335970bc8da7e', 'size_bytes': 275}; command=['C:\\Users\\h02317\\AppData\\Local\\Programs\\Python\\Python312\\python.exe', 'run_poc.py', '--input', 'C:\\Users\\h02317\\Downloads\\Wizard evaluation\\UC03_document_rag_evaluation\\fixtures\\poc_input_bundle.json']; stdout=Warning: Additional format options not available. Only PDF will be supported.
 [Torch] version: 2.9.1+cu128, cuda available: True
 Using CUDA device: NVIDIA RTX PRO 2000 Blackwell Generation Laptop GPU (devices: 1)
 Indexing 3 document(s):
@@ -1741,16 +1724,16 @@
     <t>poc_execution.json; generated output</t>
   </si>
   <si>
-    <t>[]</t>
-  </si>
-  <si>
-    <t>C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_01\poc_execution.json; parsed output paths=[]</t>
+    <t>[{"path": "output\\answer_records.json", "size_bytes": 2568, "json_parsed": true}, {"path": "output\\answer_records.json", "size_bytes": 2568, "json_parsed": true}]</t>
+  </si>
+  <si>
+    <t>C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_01\poc_execution.json; parsed output paths=['C:\\Users\\h02317\\Solution wizard evaluation\\use cases\\UC03_document_rag_evaluation\\runs\\run_01\\generated_package\\poc\\output\\answer_records.json', 'C:\\Users\\h02317\\Solution wizard evaluation\\use cases\\UC03_document_rag_evaluation\\runs\\run_01\\generated_package\\poc\\output\\answer_records.json']</t>
   </si>
   <si>
     <t>[{"path": "output\\results.json", "size_bytes": 2820, "json_parsed": true}, {"path": "output\\results.json", "size_bytes": 2820, "json_parsed": true}]</t>
   </si>
   <si>
-    <t>C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_02\poc_execution.json; parsed output paths=['C:\\Users\\h02317\\Downloads\\Wizard evaluation\\UC03_document_rag_evaluation\\runs\\run_02\\generated_package\\poc\\output\\results.json', 'C:\\Users\\h02317\\Downloads\\Wizard evaluation\\UC03_document_rag_evaluation\\runs\\run_02\\generated_package\\poc\\output\\results.json']</t>
+    <t>C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_02\poc_execution.json; parsed output paths=['C:\\Users\\h02317\\Downloads\\Wizard evaluation\\UC03_document_rag_evaluation\\runs\\run_02\\generated_package\\poc\\output\\results.json', 'C:\\Users\\h02317\\Downloads\\Wizard evaluation\\UC03_document_rag_evaluation\\runs\\run_02\\generated_package\\poc\\output\\results.json']</t>
   </si>
   <si>
     <t>EQ4-X04</t>
@@ -1765,13 +1748,16 @@
     <t>fixtures/expected_rag_results.json; poc_execution.json</t>
   </si>
   <si>
-    <t>Oracle fixture: C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\fixtures\expected_rag_results.json={"schema_version": "1.0.0", "acceptance_policy": {"authorized_answers": "Contain the required facts and at least one citation to an allowed source.", "unauthorized_answer": "Refuses because of access restrictions, contains no restricted numerical facts, and has an empty citations list.", "citation_format": "[file_name, page_number]", "page_number_basis": "1-based PDF page number"}, "expected_results": [{"query_id": "Q01", "role": "employee", "access_decision": "allowed", "required_facts": ["EUR 180 per night", "written Finance Director approval before booking when exceeded"], "required_citations": [["employee_travel_policy.pdf", 3]]}, {"query_id": "Q02", "role": "employee", "access_decision": "allowed", "required_facts": ["inspect every 250 operating hours", "replace after 1,000 operating hours or when differential pressure exceeds 1.8 bar, whichever occurs first"], "required_citations": [["mx200_maintenance_manual.pdf", 3], ["mx200_maintenance_manual.pdf", 4]]}, {"query_id": "Q03", "role": "employee", "access_decision": "denied", "required_facts": ["refusal or insufficient permission"], "forbidden_facts": ["12 percent", "22 percent", "Chief Financial Officer"], "required_citations": []}, {"query_id": "Q04", "role": "manager", "access_decision": "allowed", "required_facts": ["12 percent", "written approval from the Chief Financial Officer above the ceiling"], "required_citations": [["project_aurora_pricing_strategy.pdf", 3]]}]}; generated output evidence: C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_01\poc_execution.json outputs.</t>
+    <t>[[{"query_id": "Q01", "role": "employee", "question": "What is the maximum reimbursable hotel rate in Helsinki, and what happens if it is exceeded?", "access_decision": "allowed", "answer": "The maximum reimbursable hotel rate in Helsinki is EUR 180 per night.\n\nIf that city limit is exceeded because the only suitable room is above the limit, the traveller must explain the reason and obtain written Finance Director approval before booking. If the rate increases after an unconfirmed reservation, the booking must not be confirmed until the applicable approval has been obtained.", "citations": [["employee_travel_policy.pdf", 3], ["employee_travel_policy.pdf", 4]], "refusal_reason": null}, {"query_id": "Q02", "role": "employee", "question": "How often should the MX-200 main process filter be inspected and when must it be replaced?", "access_decision": "allowed", "answer": "The MX-200 main process filter should be inspected every 250 operating hours.\n\nIt must be replaced after 1,000 operating hours or earlier when differential pressure exceeds 1.8 bar, whichever occurs first.", "citations": [["mx200_maintenance_manual.pdf", 2], ["mx200_maintenance_manual.pdf", 3], ["mx200_maintenance_manual.pdf", 4], ["mx200_maintenance_manual.pdf", 6]], "refusal_reason": null}, {"query_id": "Q03", "role": "employee", "question": "What discount ceiling applies to Project Aurora?", "access_decision": "denied", "answer": "I'm not able to share that information -- it is restricted to a different role.", "citations": [], "refusal_reason": "The requested information is in a document not permitted for your role."}, {"query_id": "Q04", "role": "manager", "question": "What discount ceiling applies to Project Aurora and who approves an exception?", "access_decision": "allowed", "answer": "The standard discount ceiling for Project Aurora is 12 percent. Any discount above 12 percent requires written approval from the Chief Financial Officer before an offer is issued.", "citations": [["project_aurora_pricing_strategy.pdf", 2], ["project_aurora_pricing_strategy.pdf", 3]], "refusal_reason": null}], [{"query_id": "Q01", "role": "employee", "question": "What is the maximum reimbursable hotel rate in Helsinki, and what happens if it is exceeded?", "access_decision": "allowed", "answer": "The maximum reimbursable hotel rate in Helsinki is EUR 180 per night.\n\nIf that city limit is exceeded because the only suitable room is above the limit, the traveller must explain the reason and obtain written Finance Director approval before booking. If the rate increases after an unconfirmed reservation, the booking must not be confirmed until the applicable approval has been obtained.", "citations": [["employee_travel_policy.pdf", 3], ["employee_travel_policy.pdf", 4]], "refusal_reason": null}, {"query_id": "Q02", "role": "employee", "question": "How often should the MX-200 main process filter be inspected and when must it be replaced?", "access_decision": "allowed", "answer": "The MX-200 main process filter should be inspected every 250 operating hours.\n\nIt must be replaced after 1,000 operating hours or earlier when differential pressure exceeds 1.8 bar, whichever occurs first.", "citations": [["mx200_maintenance_manual.pdf", 2], ["mx200_maintenance_manual.pdf", 3], ["mx200_maintenance_manual.pdf", 4], ["mx200_maintenance_manual.pdf", 6]], "refusal_reason": null}, {"query_id": "Q03", "role": "employee", "question": "What discount ceiling applies to Project Aurora?", "access_decision": "denied", "answer": "I'm not able to share that information -- it is restricted to a different role.", "citations": [], "refusal_reason": "The requested information is in a document not permitted for your role."}, {"query_id": "Q04", "role": "manager", "question": "What discount ceiling applies to Project Aurora and who approves an exception?", "access_decision": "allowed", "answer": "The standard discount ceiling for Project Aurora is 12 percent. Any discount above 12 percent requires written approval from the Chief Financial Officer before an offer is issued.", "citations": [["project_aurora_pricing_strategy.pdf", 2], ["project_aurora_pricing_strategy.pdf", 3]], "refusal_reason": null}]]</t>
+  </si>
+  <si>
+    <t>Oracle fixture: C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\fixtures\expected_rag_results.json={"schema_version": "1.0.0", "acceptance_policy": {"authorized_answers": "Contain the required facts and at least one citation to an allowed source.", "unauthorized_answer": "Refuses because of access restrictions, contains no restricted numerical facts, and has an empty citations list.", "citation_format": "[file_name, page_number]", "page_number_basis": "1-based PDF page number"}, "expected_results": [{"query_id": "Q01", "role": "employee", "access_decision": "allowed", "required_facts": ["EUR 180 per night", "written Finance Director approval before booking when exceeded"], "required_citations": [["employee_travel_policy.pdf", 3]]}, {"query_id": "Q02", "role": "employee", "access_decision": "allowed", "required_facts": ["inspect every 250 operating hours", "replace after 1,000 operating hours or when differential pressure exceeds 1.8 bar, whichever occurs first"], "required_citations": [["mx200_maintenance_manual.pdf", 3], ["mx200_maintenance_manual.pdf", 4]]}, {"query_id": "Q03", "role": "employee", "access_decision": "denied", "required_facts": ["refusal or insufficient permission"], "forbidden_facts": ["12 percent", "22 percent", "Chief Financial Officer"], "required_citations": []}, {"query_id": "Q04", "role": "manager", "access_decision": "allowed", "required_facts": ["12 percent", "written approval from the Chief Financial Officer above the ceiling"], "required_citations": [["project_aurora_pricing_strategy.pdf", 3]]}]}; generated output evidence: C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_01\poc_execution.json outputs.</t>
   </si>
   <si>
     <t>[[{"query_id": "Q01", "role": "employee", "question": "What is the maximum reimbursable hotel rate in Helsinki, and what happens if it is exceeded?", "access_decision": "allowed", "answer": "The maximum reimbursable hotel rate in Helsinki is **EUR 180 per night** [employee_travel_policy.pdf, page 3].\n\nIf this limit is exceeded, **written approval from the Finance Director is required before booking** [employee_travel_policy.pdf, page 3]. If only a suitable room exceeds the city limit, the traveller must **explain the reason and obtain that written approval before booking** [employee_travel_policy.pdf, page 3].", "citations": [["employee_travel_policy.pdf", 3], ["employee_travel_policy.pdf", 4]], "refusal_reason": null}, {"query_id": "Q02", "role": "employee", "question": "How often should the MX-200 main process filter be inspected and when must it be replaced?", "access_decision": "allowed", "answer": "The MX-200 main process filter should be **inspected every 250 operating hours** [mx200_maintenance_manual.pdf, page 3].\n\nIt must be **replaced after 1,000 operating hours or earlier if the differential pressure exceeds 1.8 bar, whichever comes first** [mx200_maintenance_manual.pdf, page 4].", "citations": [["mx200_maintenance_manual.pdf", 4], ["mx200_maintenance_manual.pdf", 3], ["mx200_maintenance_manual.pdf", 6], ["mx200_maintenance_manual.pdf", 2]], "refusal_reason": null}, {"query_id": "Q03", "role": "employee", "question": "What discount ceiling applies to Project Aurora?", "access_decision": "denied", "answer": "Access denied. The information you requested is contained in a document that your role is not authorised to access.", "citations": [], "refusal_reason": "The requested information exists in a management-confidential document. Access is restricted to authorised roles only."}, {"query_id": "Q04", "role": "manager", "question": "What discount ceiling applies to Project Aurora and who approves an exception?", "access_decision": "allowed", "answer": "The standard discount ceiling for Project Aurora is 12 percent. Any discount above 12 percent requires written approval from the Chief Financial Officer before an offer is issued [project_aurora_pricing_strategy.pdf, page 3].", "citations": [["project_aurora_pricing_strategy.pdf", 3], ["project_aurora_pricing_strategy.pdf", 2]], "refusal_reason": null}], [{"query_id": "Q01", "role": "employee", "question": "What is the maximum reimbursable hotel rate in Helsinki, and what happens if it is exceeded?", "access_decision": "allowed", "answer": "The maximum reimbursable hotel rate in Helsinki is **EUR 180 per night** [employee_travel_policy.pdf, page 3].\n\nIf this limit is exceeded, **written approval from the Finance Director is required before booking** [employee_travel_policy.pdf, page 3]. If only a suitable room exceeds the city limit, the traveller must **explain the reason and obtain that written approval before booking** [employee_travel_policy.pdf, page 3].", "citations": [["employee_travel_policy.pdf", 3], ["employee_travel_policy.pdf", 4]], "refusal_reason": null}, {"query_id": "Q02", "role": "employee", "question": "How often should the MX-200 main process filter be inspected and when must it be replaced?", "access_decision": "allowed", "answer": "The MX-200 main process filter should be **inspected every 250 operating hours** [mx200_maintenance_manual.pdf, page 3].\n\nIt must be **replaced after 1,000 operating hours or earlier if the differential pressure exceeds 1.8 bar, whichever comes first** [mx200_maintenance_manual.pdf, page 4].", "citations": [["mx200_maintenance_manual.pdf", 4], ["mx200_maintenance_manual.pdf", 3], ["mx200_maintenance_manual.pdf", 6], ["mx200_maintenance_manual.pdf", 2]], "refusal_reason": null}, {"query_id": "Q03", "role": "employee", "question": "What discount ceiling applies to Project Aurora?", "access_decision": "denied", "answer": "Access denied. The information you requested is contained in a document that your role is not authorised to access.", "citations": [], "refusal_reason": "The requested information exists in a management-confidential document. Access is restricted to authorised roles only."}, {"query_id": "Q04", "role": "manager", "question": "What discount ceiling applies to Project Aurora and who approves an exception?", "access_decision": "allowed", "answer": "The standard discount ceiling for Project Aurora is 12 percent. Any discount above 12 percent requires written approval from the Chief Financial Officer before an offer is issued [project_aurora_pricing_strategy.pdf, page 3].", "citations": [["project_aurora_pricing_strategy.pdf", 3], ["project_aurora_pricing_strategy.pdf", 2]], "refusal_reason": null}]]</t>
   </si>
   <si>
-    <t>Oracle fixture: C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\fixtures\expected_rag_results.json={"schema_version": "1.0.0", "acceptance_policy": {"authorized_answers": "Contain the required facts and at least one citation to an allowed source.", "unauthorized_answer": "Refuses because of access restrictions, contains no restricted numerical facts, and has an empty citations list.", "citation_format": "[file_name, page_number]", "page_number_basis": "1-based PDF page number"}, "expected_results": [{"query_id": "Q01", "role": "employee", "access_decision": "allowed", "required_facts": ["EUR 180 per night", "written Finance Director approval before booking when exceeded"], "required_citations": [["employee_travel_policy.pdf", 3]]}, {"query_id": "Q02", "role": "employee", "access_decision": "allowed", "required_facts": ["inspect every 250 operating hours", "replace after 1,000 operating hours or when differential pressure exceeds 1.8 bar, whichever occurs first"], "required_citations": [["mx200_maintenance_manual.pdf", 3], ["mx200_maintenance_manual.pdf", 4]]}, {"query_id": "Q03", "role": "employee", "access_decision": "denied", "required_facts": ["refusal or insufficient permission"], "forbidden_facts": ["12 percent", "22 percent", "Chief Financial Officer"], "required_citations": []}, {"query_id": "Q04", "role": "manager", "access_decision": "allowed", "required_facts": ["12 percent", "written approval from the Chief Financial Officer above the ceiling"], "required_citations": [["project_aurora_pricing_strategy.pdf", 3]]}]}; generated output evidence: C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_02\poc_execution.json outputs.</t>
+    <t>Oracle fixture: C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\fixtures\expected_rag_results.json={"schema_version": "1.0.0", "acceptance_policy": {"authorized_answers": "Contain the required facts and at least one citation to an allowed source.", "unauthorized_answer": "Refuses because of access restrictions, contains no restricted numerical facts, and has an empty citations list.", "citation_format": "[file_name, page_number]", "page_number_basis": "1-based PDF page number"}, "expected_results": [{"query_id": "Q01", "role": "employee", "access_decision": "allowed", "required_facts": ["EUR 180 per night", "written Finance Director approval before booking when exceeded"], "required_citations": [["employee_travel_policy.pdf", 3]]}, {"query_id": "Q02", "role": "employee", "access_decision": "allowed", "required_facts": ["inspect every 250 operating hours", "replace after 1,000 operating hours or when differential pressure exceeds 1.8 bar, whichever occurs first"], "required_citations": [["mx200_maintenance_manual.pdf", 3], ["mx200_maintenance_manual.pdf", 4]]}, {"query_id": "Q03", "role": "employee", "access_decision": "denied", "required_facts": ["refusal or insufficient permission"], "forbidden_facts": ["12 percent", "22 percent", "Chief Financial Officer"], "required_citations": []}, {"query_id": "Q04", "role": "manager", "access_decision": "allowed", "required_facts": ["12 percent", "written approval from the Chief Financial Officer above the ceiling"], "required_citations": [["project_aurora_pricing_strategy.pdf", 3]]}]}; generated output evidence: C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_02\poc_execution.json outputs.</t>
   </si>
   <si>
     <t>PoC recovery diagnostic</t>
@@ -1792,10 +1778,10 @@
     <t>Original execution successful</t>
   </si>
   <si>
-    <t>C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_01\poc_recovery.json; baseline=C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_01\poc_execution.json; attempts=[{"attempt": 1, "successful": true, "execution_file": "C:\\Users\\h02317\\Downloads\\Wizard evaluation\\UC03_document_rag_evaluation\\runs\\run_01\\refinement\\attempt_01\\poc_execution.json", "conversation_file": "C:\\Users\\h02317\\Downloads\\Wizard evaluation\\UC03_document_rag_evaluation\\runs\\run_01\\refinement\\attempt_01\\conversation.txt"}]</t>
-  </si>
-  <si>
-    <t>C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_02\poc_recovery.json; baseline=C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_02\poc_execution.json; attempts=[]</t>
+    <t>C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_01\poc_recovery.json; baseline=C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_01\poc_execution.json; attempts=[{"attempt": 1, "successful": true, "execution_file": "C:\\Users\\h02317\\Solution wizard evaluation\\use cases\\UC03_document_rag_evaluation\\runs\\run_01\\refinement\\attempt_01\\poc_execution.json", "conversation_file": "C:\\Users\\h02317\\Solution wizard evaluation\\use cases\\UC03_document_rag_evaluation\\runs\\run_01\\refinement\\attempt_01\\conversation.txt"}]</t>
+  </si>
+  <si>
+    <t>C:\Users\h02317\Solution wizard evaluation\use cases\UC03_document_rag_evaluation\runs\run_02\poc_recovery.json; baseline=C:\Users\h02317\Downloads\Wizard evaluation\UC03_document_rag_evaluation\runs\run_02\poc_execution.json; attempts=[]</t>
   </si>
   <si>
     <t>Yes or No</t>
@@ -1819,9 +1805,6 @@
     <t>Shows whether recovery ultimately produced an executable PoC.</t>
   </si>
   <si>
-    <t>recovered</t>
-  </si>
-  <si>
     <t>successful_original</t>
   </si>
   <si>
@@ -1831,16 +1814,25 @@
     <t>Stop after first success or after refinement attempt 3.</t>
   </si>
   <si>
-    <t xml:space="preserve">The wizard did not cover this question. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">The wizard did not cover this question in the first run. </t>
-  </si>
-  <si>
     <t>Azure OpenAI generation model gpt-5.4, temperature 1.0, reasoning effort medium, plus a supported Azure OpenAI embedding model.</t>
   </si>
   <si>
-    <t>azure_openai; answer_model gpt-5.4; temperature 1.0; reasoning_effort medium; embedding model from_env_AZURE_EMBEDDING_DEPLOYMENT / text-embedding-3-large in config</t>
+    <t xml:space="preserve">No schema exists in this use case. The RAG prompt does not need to be saved for this use case. </t>
+  </si>
+  <si>
+    <t>Validator exit code 0.</t>
+  </si>
+  <si>
+    <t>Resolution: auto-discovered at C:\Users\h02317\gaik-toolkit\implementation_layer\solution_wizard\scripts\validate_blueprint.py; command: ['C:\\Users\\h02317\\AppData\\Local\\Programs\\Python\\Python312\\python.exe', 'C:\\Users\\h02317\\gaik-toolkit\\implementation_layer\\solution_wizard\\scripts\\validate_blueprint.py', '--blueprint', 'C:\\Users\\h02317\\Solution wizard evaluation\\use cases\\UC03_document_rag_evaluation\\runs\\run_01\\generated_package\\use_case.blueprint.json']; cwd: C:\Users\h02317\gaik-toolkit\implementation_layer\solution_wizard; output: Validation PASSED
+  WARNING Rule 11: High-impact assumption 'assumption_002' is still unconfirmed. Resolve before production packaging. Text: "The exact Azure OpenAI embedding deployment name was not specified; the PoC will read it from an environment variable and default to a model compatible with RAGWorkflow (text-embedding-3-large)."
+  WARNING Rule 11: High-impact assumption 'assumption_003' is still unconfirmed. Resolve before production packaging. Text: "No exact data-retention period was specified for PoC outputs; recorded as not_specified."
+  WARNING Rule 11: High-impact assumption 'assumption_005' is still unconfirmed. Resolve before production packaging. Text: "Whether real production documents (beyond the synthetic PoC fixtures) contain personal data is unknown; this is recorded as 'unknown' in governance.data_handling and will block production packaging until confirmed."</t>
+  </si>
+  <si>
+    <t>Resolution: auto-discovered at C:\Users\h02317\gaik-toolkit\implementation_layer\solution_wizard\scripts\validate_blueprint.py; command: ['C:\\Users\\h02317\\AppData\\Local\\Programs\\Python\\Python312\\python.exe', 'C:\\Users\\h02317\\gaik-toolkit\\implementation_layer\\solution_wizard\\scripts\\validate_blueprint.py', '--blueprint', 'C:\\Users\\h02317\\Solution wizard evaluation\\use cases\\UC03_document_rag_evaluation\\runs\\run_02\\generated_package\\use_case.blueprint.json']; cwd: C:\Users\h02317\gaik-toolkit\implementation_layer\solution_wizard; output: Validation PASSED
+  WARNING Rule 11: High-impact assumption 'assumption_001' is still unconfirmed. Resolve before production packaging. Text: "Embedding deployment name for Azure OpenAI is provided via environment variable AZURE_OPENAI_EMBEDDING_DEPLOYMENT. The specific model name is not user-confirmed."
+  WARNING Rule 11: High-impact assumption 'assumption_002' is still unconfirmed. Resolve before production packaging. Text: "RAGWorkflow uses a Chroma vector store (persist=True) for the PoC. The RBAC role filter is implemented as a Chroma metadata filter on the allowed_roles field, applied before similarity retrieval."
+  WARNING Rule 11: High-impact assumption 'assumption_005' is still unconfirmed. Resolve before production packaging. Text: "The documents are assumed not to contain personal data. The management-confidential document is commercially sensitive but not personal data. This affects governance.data_handling.contains_personal_data."</t>
   </si>
 </sst>
 </file>
@@ -2450,24 +2442,18 @@
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:14" ht="24" customHeight="1">
+    <row r="5" spans="1:14" ht="15" customHeight="1">
       <c r="A5" s="6" t="s">
         <v>31</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="7">
-        <v>0.9</v>
-      </c>
-      <c r="D5" s="7">
-        <v>0.93</v>
-      </c>
-      <c r="E5" s="7">
-        <v>0.92</v>
-      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
       <c r="F5" s="6">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="G5" s="6">
         <v>84</v>
@@ -2476,24 +2462,18 @@
         <v>46</v>
       </c>
     </row>
-    <row r="6" spans="1:14" ht="30" customHeight="1">
+    <row r="6" spans="1:14" ht="15" customHeight="1">
       <c r="A6" s="6" t="s">
         <v>33</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="C6" s="7">
-        <v>1</v>
-      </c>
-      <c r="D6" s="7">
-        <v>1</v>
-      </c>
-      <c r="E6" s="7">
-        <v>1</v>
-      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
       <c r="F6" s="6">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="G6" s="6">
         <v>18</v>
@@ -2502,24 +2482,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:14" ht="24.75" customHeight="1">
+    <row r="7" spans="1:14" ht="15" customHeight="1">
       <c r="A7" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="C7" s="7">
-        <v>1</v>
-      </c>
-      <c r="D7" s="7">
-        <v>1</v>
-      </c>
-      <c r="E7" s="7">
-        <v>1</v>
-      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
       <c r="F7" s="6">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G7" s="6">
         <v>16</v>
@@ -2528,24 +2502,18 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="22.5" customHeight="1">
+    <row r="8" spans="1:14" ht="15" customHeight="1">
       <c r="A8" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="6">
         <v>0</v>
-      </c>
-      <c r="D8" s="7">
-        <v>1</v>
-      </c>
-      <c r="E8" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="F8" s="6">
-        <v>8</v>
       </c>
       <c r="G8" s="6">
         <v>8</v>
@@ -2610,7 +2578,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="13" spans="1:14" ht="90.75" customHeight="1">
+    <row r="13" spans="1:14" ht="52.7" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>65</v>
       </c>
@@ -2646,7 +2614,6 @@
     <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2749,7 +2716,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="104.25" customHeight="1">
+    <row r="4" spans="1:14" ht="41.25" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>86</v>
       </c>
@@ -2778,628 +2745,628 @@
         <v>86</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="1:14" ht="26.45" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N4" s="3"/>
-    </row>
-    <row r="5" spans="1:14" ht="103.5" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>90</v>
       </c>
       <c r="F5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="L5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" spans="1:14" ht="42.75" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J5" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N5" s="3"/>
-    </row>
-    <row r="6" spans="1:14" ht="146.25" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>105</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>90</v>
       </c>
       <c r="F6" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="L6" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:14" ht="61.5" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J6" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="L6" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N6" s="3"/>
-    </row>
-    <row r="7" spans="1:14" ht="86.25" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="H7" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="L7" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N7" s="3"/>
+    </row>
+    <row r="8" spans="1:14" ht="15" customHeight="1">
+      <c r="A8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J7" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>117</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N7" s="3"/>
-    </row>
-    <row r="8" spans="1:14" ht="88.5" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>120</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>90</v>
       </c>
       <c r="F8" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="L8" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N8" s="3"/>
+    </row>
+    <row r="9" spans="1:14" ht="26.45" customHeight="1">
+      <c r="A9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J8" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="L8" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N8" s="3"/>
-    </row>
-    <row r="9" spans="1:14" ht="60" customHeight="1">
-      <c r="A9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B9" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="F9" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="G9" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="E9" s="3" t="s">
+      <c r="H9" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="F9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="L9" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N9" s="3"/>
+    </row>
+    <row r="10" spans="1:14" ht="26.45" customHeight="1">
+      <c r="A10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B10" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="H9" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" ht="68.25" customHeight="1">
-      <c r="A10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="E10" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="E10" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="G10" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="H10" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J10" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="H10" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="L10" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N10" s="3"/>
+    </row>
+    <row r="11" spans="1:14" ht="73.5" customHeight="1">
+      <c r="A11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B11" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="L10" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N10" s="3"/>
-    </row>
-    <row r="11" spans="1:14" ht="151.5" customHeight="1">
-      <c r="A11" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="E11" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="F11" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="F11" s="3" t="s">
+      <c r="G11" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="H11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J11" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="H11" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="L11" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" ht="39.6" customHeight="1">
+      <c r="A12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B12" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="L11" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" ht="95.25" customHeight="1">
-      <c r="A12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="D12" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="E12" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E12" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="G12" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="H12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="L12" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N12" s="3"/>
+    </row>
+    <row r="13" spans="1:14" ht="15" customHeight="1">
+      <c r="A13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="H12" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="K12" s="3" t="s">
+      <c r="C13" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="L12" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N12" s="3"/>
-    </row>
-    <row r="13" spans="1:14" ht="100.5" customHeight="1">
-      <c r="A13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="D13" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="E13" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="G13" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E13" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F13" s="3" t="s">
+      <c r="H13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="K13" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="H13" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J13" s="3" t="s">
+      <c r="L13" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N13" s="3"/>
+    </row>
+    <row r="14" spans="1:14" ht="15" customHeight="1">
+      <c r="A14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B14" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="K13" s="3" t="s">
+      <c r="C14" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="L13" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N13" s="3"/>
-    </row>
-    <row r="14" spans="1:14" ht="86.25" customHeight="1">
-      <c r="A14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="D14" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="E14" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="H14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="H14" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J14" s="3" t="s">
+      <c r="L14" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N14" s="3"/>
+    </row>
+    <row r="15" spans="1:14" ht="26.45" customHeight="1">
+      <c r="A15" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="K14" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="L14" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" ht="116.25" customHeight="1">
-      <c r="A15" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="G15" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="H15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="K15" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="H15" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J15" s="3" t="s">
+      <c r="L15" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N15" s="3"/>
+    </row>
+    <row r="16" spans="1:14" ht="26.45" customHeight="1">
+      <c r="A16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="L15" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" ht="102" customHeight="1">
-      <c r="A16" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="G16" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="H16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="K16" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="H16" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J16" s="3" t="s">
+      <c r="L16" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="1:14" ht="26.45" customHeight="1">
+      <c r="A17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B17" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="K16" s="3" t="s">
+      <c r="C17" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="L16" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="1:14" ht="113.25" customHeight="1">
-      <c r="A17" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B17" s="3" t="s">
+      <c r="D17" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="E17" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="G17" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="H17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="K17" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="H17" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J17" s="3" t="s">
+      <c r="L17" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N17" s="3"/>
+    </row>
+    <row r="18" spans="1:14" ht="26.45" customHeight="1">
+      <c r="A18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B18" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="K17" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="L17" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N17" s="3"/>
-    </row>
-    <row r="18" spans="1:14" ht="170.25" customHeight="1">
-      <c r="A18" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B18" s="3" t="s">
+      <c r="D18" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="E18" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D18" s="3" t="s">
+      <c r="G18" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="H18" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="G18" s="3" t="s">
+      <c r="K18" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="H18" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J18" s="3" t="s">
+      <c r="L18" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N18" s="3"/>
+    </row>
+    <row r="19" spans="1:14" ht="15" customHeight="1">
+      <c r="A19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B19" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="K18" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="L18" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N18" s="3"/>
-    </row>
-    <row r="19" spans="1:14" ht="115.5" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="E19" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="G19" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>198</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>93</v>
@@ -3411,382 +3378,382 @@
         <v>197</v>
       </c>
       <c r="K19" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="L19" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="1:14" ht="26.45" customHeight="1">
+      <c r="A20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="L19" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="1:14" ht="132" customHeight="1">
-      <c r="A20" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B20" s="3" t="s">
+      <c r="C20" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="D20" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="E20" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="E20" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="G20" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="G20" s="3" t="s">
+      <c r="K20" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="H20" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J20" s="3" t="s">
+      <c r="L20" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N20" s="3"/>
+    </row>
+    <row r="21" spans="1:14" ht="26.45" customHeight="1">
+      <c r="A21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="K20" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="L20" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N20" s="3"/>
-    </row>
-    <row r="21" spans="1:14" ht="132.75" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B21" s="3" t="s">
+      <c r="D21" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="E21" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F21" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D21" s="3" t="s">
+      <c r="G21" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="H21" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="G21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="H21" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J21" s="3" t="s">
+      <c r="L21" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N21" s="3"/>
+    </row>
+    <row r="22" spans="1:14" ht="26.45" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B22" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="K21" s="3" t="s">
+      <c r="C22" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="L21" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N21" s="3"/>
-    </row>
-    <row r="22" spans="1:14" ht="119.25" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B22" s="3" t="s">
+      <c r="D22" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="E22" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="D22" s="3" t="s">
+      <c r="G22" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="E22" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F22" s="3" t="s">
+      <c r="H22" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J22" s="3" t="s">
+      <c r="L22" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N22" s="3"/>
+    </row>
+    <row r="23" spans="1:14" ht="46.5" customHeight="1">
+      <c r="A23" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B23" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="K22" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="L22" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N22" s="3"/>
-    </row>
-    <row r="23" spans="1:14" ht="58.5" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B23" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="D23" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="E23" s="3" t="s">
+      <c r="G23" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="F23" s="3" t="s">
+      <c r="H23" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="G23" s="3" t="s">
+      <c r="K23" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="H23" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J23" s="3" t="s">
+      <c r="L23" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N23" s="3"/>
+    </row>
+    <row r="24" spans="1:14" ht="55.5" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B24" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="K23" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="L23" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N23" s="3"/>
-    </row>
-    <row r="24" spans="1:14" ht="156" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B24" s="3" t="s">
+      <c r="D24" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="E24" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="D24" s="3" t="s">
+      <c r="G24" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="E24" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F24" s="3" t="s">
+      <c r="H24" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="G24" s="3" t="s">
+      <c r="K24" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="H24" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J24" s="3" t="s">
+      <c r="L24" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N24" s="3"/>
+    </row>
+    <row r="25" spans="1:14" ht="86.25" customHeight="1">
+      <c r="A25" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B25" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="K24" s="3" t="s">
+      <c r="C25" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="L24" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N24" s="3"/>
-    </row>
-    <row r="25" spans="1:14" ht="199.5" customHeight="1">
-      <c r="A25" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B25" s="3" t="s">
+      <c r="D25" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="E25" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F25" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="D25" s="3" t="s">
+      <c r="G25" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F25" s="3" t="s">
+      <c r="H25" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="K25" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="H25" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J25" s="3" t="s">
+      <c r="L25" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N25" s="3"/>
+    </row>
+    <row r="26" spans="1:14" ht="48" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B26" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="K25" s="3" t="s">
+      <c r="C26" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="L25" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N25" s="3"/>
-    </row>
-    <row r="26" spans="1:14" ht="63" customHeight="1">
-      <c r="A26" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B26" s="3" t="s">
+      <c r="D26" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="E26" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="D26" s="3" t="s">
+      <c r="G26" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="E26" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F26" s="3" t="s">
+      <c r="H26" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="K26" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="H26" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J26" s="3" t="s">
+      <c r="L26" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="N26" s="3"/>
+    </row>
+    <row r="27" spans="1:14" ht="60.75" customHeight="1">
+      <c r="A27" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B27" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="K26" s="3" t="s">
+      <c r="C27" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="L26" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N26" s="3"/>
-    </row>
-    <row r="27" spans="1:14" ht="166.5" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B27" s="3" t="s">
+      <c r="D27" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="E27" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F27" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="D27" s="3" t="s">
+      <c r="G27" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="E27" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F27" s="3" t="s">
+      <c r="H27" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="K27" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="H27" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J27" s="3" t="s">
+      <c r="L27" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N27" s="3"/>
+    </row>
+    <row r="28" spans="1:14" ht="55.5" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B28" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="K27" s="3" t="s">
+      <c r="C28" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="L27" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N27" s="3"/>
-    </row>
-    <row r="28" spans="1:14" ht="112.5" customHeight="1">
-      <c r="A28" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B28" s="3" t="s">
+      <c r="D28" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="E28" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F28" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="D28" s="3" t="s">
+      <c r="G28" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="E28" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="G28" s="3" t="s">
+      <c r="H28" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="K28" s="3" t="s">
         <v>260</v>
@@ -3795,13 +3762,11 @@
         <v>93</v>
       </c>
       <c r="M28" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N28" s="3" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" ht="150" customHeight="1">
+        <v>86</v>
+      </c>
+      <c r="N28" s="3"/>
+    </row>
+    <row r="29" spans="1:14" ht="57" customHeight="1">
       <c r="A29" s="3" t="s">
         <v>86</v>
       </c>
@@ -3815,7 +3780,7 @@
         <v>263</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>264</v>
@@ -3843,7 +3808,7 @@
       </c>
       <c r="N29" s="3"/>
     </row>
-    <row r="30" spans="1:14" ht="64.5" customHeight="1">
+    <row r="30" spans="1:14" ht="15" customHeight="1">
       <c r="A30" s="3" t="s">
         <v>86</v>
       </c>
@@ -3857,7 +3822,7 @@
         <v>270</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>271</v>
@@ -3872,10 +3837,10 @@
         <v>86</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="L30" s="4" t="s">
         <v>93</v>
@@ -3885,27 +3850,27 @@
       </c>
       <c r="N30" s="3"/>
     </row>
-    <row r="31" spans="1:14" ht="127.5" customHeight="1">
+    <row r="31" spans="1:14" ht="52.7" customHeight="1">
       <c r="A31" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H31" s="4" t="s">
         <v>93</v>
@@ -3914,10 +3879,10 @@
         <v>86</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="L31" s="4" t="s">
         <v>93</v>
@@ -3925,580 +3890,575 @@
       <c r="M31" s="3" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="32" spans="1:14" ht="135.75" customHeight="1">
+      <c r="N31" s="3"/>
+    </row>
+    <row r="32" spans="1:14" ht="80.25" customHeight="1">
       <c r="A32" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="H32" s="4" t="s">
         <v>93</v>
       </c>
       <c r="I32" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N32" s="3"/>
+    </row>
+    <row r="33" spans="1:14" ht="53.25" customHeight="1">
+      <c r="A33" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="L33" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N33" s="3"/>
+    </row>
+    <row r="34" spans="1:14" ht="52.7" customHeight="1">
+      <c r="A34" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="H34" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="L34" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N34" s="3"/>
+    </row>
+    <row r="35" spans="1:14" ht="52.7" customHeight="1">
+      <c r="A35" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="L35" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N35" s="3"/>
+    </row>
+    <row r="36" spans="1:14" ht="39.6" customHeight="1">
+      <c r="A36" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="L36" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N36" s="3"/>
+    </row>
+    <row r="37" spans="1:14" ht="52.7" customHeight="1">
+      <c r="A37" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="L37" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N37" s="3"/>
+    </row>
+    <row r="38" spans="1:14" ht="15" customHeight="1">
+      <c r="A38" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="H38" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="L38" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N38" s="3"/>
+    </row>
+    <row r="39" spans="1:14" ht="92.45" customHeight="1">
+      <c r="A39" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="L39" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="1:14" ht="39.6" customHeight="1">
+      <c r="A40" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="L40" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="1:14" ht="89.25" customHeight="1">
+      <c r="A41" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="L41" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N41" s="3"/>
+    </row>
+    <row r="42" spans="1:14" ht="79.150000000000006" customHeight="1">
+      <c r="A42" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="L42" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N42" s="3"/>
+    </row>
+    <row r="43" spans="1:14" ht="66" customHeight="1">
+      <c r="A43" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="L43" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N43" s="3"/>
+    </row>
+    <row r="44" spans="1:14" ht="100.5" customHeight="1">
+      <c r="A44" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="L44" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N44" s="3"/>
+    </row>
+    <row r="45" spans="1:14" ht="165" customHeight="1">
+      <c r="A45" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="F45" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" ht="111.75" customHeight="1">
-      <c r="A33" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="H33" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="L33" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N33" s="3"/>
-    </row>
-    <row r="34" spans="1:14" ht="108" customHeight="1">
-      <c r="A34" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="H34" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="L34" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N34" s="3"/>
-    </row>
-    <row r="35" spans="1:14" ht="145.5" customHeight="1">
-      <c r="A35" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="L35" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N35" s="3"/>
-    </row>
-    <row r="36" spans="1:14" ht="180" customHeight="1">
-      <c r="A36" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="L36" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N36" s="3"/>
-    </row>
-    <row r="37" spans="1:14" ht="168" customHeight="1">
-      <c r="A37" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="L37" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N37" s="3" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" ht="149.25" customHeight="1">
-      <c r="A38" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="H38" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="L38" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N38" s="3"/>
-    </row>
-    <row r="39" spans="1:14" ht="168.75" customHeight="1">
-      <c r="A39" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>582</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>583</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="H39" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="L39" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="1:14" ht="134.25" customHeight="1">
-      <c r="A40" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="H40" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="L40" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="1:14" ht="126" customHeight="1">
-      <c r="A41" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="L41" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N41" s="3"/>
-    </row>
-    <row r="42" spans="1:14" ht="214.5" customHeight="1">
-      <c r="A42" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="L42" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N42" s="3"/>
-    </row>
-    <row r="43" spans="1:14" ht="120.75" customHeight="1">
-      <c r="A43" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="L43" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="N43" s="3" t="s">
-        <v>580</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14" ht="173.25" customHeight="1">
-      <c r="A44" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="L44" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N44" s="3"/>
-    </row>
-    <row r="45" spans="1:14" ht="299.25" customHeight="1">
-      <c r="A45" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>370</v>
-      </c>
       <c r="G45" s="3" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="H45" s="4" t="s">
         <v>93</v>
@@ -4507,10 +4467,10 @@
         <v>86</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="L45" s="4" t="s">
         <v>93</v>
@@ -4555,7 +4515,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="27.95" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -4573,7 +4533,7 @@
     </row>
     <row r="2" spans="1:14" ht="39.950000000000003" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -4589,7 +4549,7 @@
       <c r="M2" s="10"/>
       <c r="N2" s="10"/>
     </row>
-    <row r="3" spans="1:14" ht="40.5" customHeight="1">
+    <row r="3" spans="1:14" ht="15" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>72</v>
       </c>
@@ -4633,27 +4593,27 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="142.5" customHeight="1">
+    <row r="4" spans="1:14" ht="120.75" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>93</v>
@@ -4662,40 +4622,40 @@
         <v>86</v>
       </c>
       <c r="J4" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="1:14" ht="87.75" customHeight="1">
+      <c r="A5" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="K4" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N4" s="3"/>
-    </row>
-    <row r="5" spans="1:14" ht="113.25" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>376</v>
-      </c>
       <c r="B5" s="3" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>93</v>
@@ -4704,10 +4664,10 @@
         <v>86</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>93</v>
@@ -4717,27 +4677,27 @@
       </c>
       <c r="N5" s="3"/>
     </row>
-    <row r="6" spans="1:14" ht="296.25" customHeight="1">
+    <row r="6" spans="1:14" ht="130.5" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>93</v>
@@ -4746,10 +4706,10 @@
         <v>86</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>93</v>
@@ -4794,7 +4754,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="27.95" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -4812,7 +4772,7 @@
     </row>
     <row r="2" spans="1:14" ht="39.950000000000003" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -4872,27 +4832,27 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="144" customHeight="1">
+    <row r="4" spans="1:14" ht="46.5" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>93</v>
@@ -4901,10 +4861,10 @@
         <v>86</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>93</v>
@@ -4914,27 +4874,27 @@
       </c>
       <c r="N4" s="3"/>
     </row>
-    <row r="5" spans="1:14" ht="168.75" customHeight="1">
+    <row r="5" spans="1:14" ht="48" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>93</v>
@@ -4943,10 +4903,10 @@
         <v>86</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="L5" s="4" t="s">
         <v>93</v>
@@ -4956,27 +4916,27 @@
       </c>
       <c r="N5" s="3"/>
     </row>
-    <row r="6" spans="1:14" ht="306.75" customHeight="1">
+    <row r="6" spans="1:14" ht="76.5" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>93</v>
@@ -4985,10 +4945,10 @@
         <v>86</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
       <c r="L6" s="4" t="s">
         <v>93</v>
@@ -4998,27 +4958,27 @@
       </c>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:14" ht="172.5" customHeight="1">
+    <row r="7" spans="1:14" ht="63" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>419</v>
-      </c>
       <c r="F7" s="3" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
       <c r="H7" s="4" t="s">
         <v>93</v>
@@ -5027,10 +4987,10 @@
         <v>86</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>93</v>
@@ -5040,27 +5000,27 @@
       </c>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:14" ht="263.25" customHeight="1">
+    <row r="8" spans="1:14" ht="52.7" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>93</v>
@@ -5069,10 +5029,10 @@
         <v>86</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
       <c r="L8" s="4" t="s">
         <v>93</v>
@@ -5082,27 +5042,27 @@
       </c>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="1:14" ht="372.75" customHeight="1">
+    <row r="9" spans="1:14" ht="70.5" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="H9" s="4" t="s">
         <v>93</v>
@@ -5111,10 +5071,10 @@
         <v>86</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="L9" s="4" t="s">
         <v>93</v>
@@ -5124,27 +5084,27 @@
       </c>
       <c r="N9" s="3"/>
     </row>
-    <row r="10" spans="1:14" ht="327" customHeight="1">
+    <row r="10" spans="1:14" ht="88.5" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>93</v>
@@ -5153,10 +5113,10 @@
         <v>86</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="L10" s="4" t="s">
         <v>93</v>
@@ -5166,27 +5126,27 @@
       </c>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="1:14" ht="208.5" customHeight="1">
+    <row r="11" spans="1:14" ht="84" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>93</v>
@@ -5195,10 +5155,10 @@
         <v>86</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="L11" s="4" t="s">
         <v>93</v>
@@ -5208,27 +5168,27 @@
       </c>
       <c r="N11" s="3"/>
     </row>
-    <row r="12" spans="1:14" ht="409.5" customHeight="1">
+    <row r="12" spans="1:14" ht="92.25" customHeight="1">
       <c r="A12" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>93</v>
@@ -5237,10 +5197,10 @@
         <v>86</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
       <c r="L12" s="4" t="s">
         <v>93</v>
@@ -5285,7 +5245,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="27.95" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -5303,7 +5263,7 @@
     </row>
     <row r="2" spans="1:14" ht="39.950000000000003" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -5363,240 +5323,240 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="74.25" customHeight="1">
+    <row r="4" spans="1:14" ht="57.75" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>86</v>
       </c>
       <c r="N4" s="3"/>
     </row>
-    <row r="5" spans="1:14" ht="269.25" customHeight="1">
+    <row r="5" spans="1:14" ht="26.45" customHeight="1">
       <c r="A5" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="H5" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>474</v>
-      </c>
       <c r="I5" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>481</v>
+        <v>580</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>483</v>
+        <v>582</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>86</v>
       </c>
       <c r="N5" s="3"/>
     </row>
-    <row r="6" spans="1:14" ht="73.5" customHeight="1">
+    <row r="6" spans="1:14" ht="68.25" customHeight="1">
       <c r="A6" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="M6" s="3" t="s">
         <v>86</v>
       </c>
       <c r="N6" s="3"/>
     </row>
-    <row r="7" spans="1:14" ht="93.75" customHeight="1">
+    <row r="7" spans="1:14" ht="59.25" customHeight="1">
       <c r="A7" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="I7" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="M7" s="3" t="s">
         <v>86</v>
       </c>
       <c r="N7" s="3"/>
     </row>
-    <row r="8" spans="1:14" ht="85.5" customHeight="1">
+    <row r="8" spans="1:14" ht="62.25" customHeight="1">
       <c r="A8" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="I8" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="M8" s="3" t="s">
         <v>86</v>
       </c>
       <c r="N8" s="3"/>
     </row>
-    <row r="9" spans="1:14" ht="147.75" customHeight="1">
+    <row r="9" spans="1:14" ht="157.5" customHeight="1">
       <c r="A9" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="I9" s="3" t="s">
         <v>86</v>
@@ -5605,17 +5565,19 @@
         <v>511</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>513</v>
+        <v>479</v>
       </c>
       <c r="M9" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="N9" s="3"/>
-    </row>
-    <row r="10" spans="1:14" ht="120" customHeight="1">
+      <c r="N9" s="3" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" ht="60.75" customHeight="1">
       <c r="A10" s="3" t="s">
         <v>86</v>
       </c>
@@ -5638,7 +5600,7 @@
         <v>519</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>86</v>
@@ -5650,14 +5612,14 @@
         <v>520</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="M10" s="3" t="s">
         <v>86</v>
       </c>
       <c r="N10" s="3"/>
     </row>
-    <row r="11" spans="1:14" ht="68.25" customHeight="1">
+    <row r="11" spans="1:14" ht="60" customHeight="1">
       <c r="A11" s="3" t="s">
         <v>86</v>
       </c>
@@ -5680,19 +5642,19 @@
         <v>526</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>513</v>
+        <v>479</v>
       </c>
       <c r="I11" s="3" t="s">
         <v>86</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="K11" s="3" t="s">
-        <v>528</v>
-      </c>
       <c r="L11" s="4" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
       <c r="M11" s="3" t="s">
         <v>86</v>
@@ -5734,7 +5696,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="27.95" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -5752,7 +5714,7 @@
     </row>
     <row r="2" spans="1:14" ht="39.950000000000003" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -5812,165 +5774,165 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="1:14" ht="409.5" customHeight="1">
+    <row r="4" spans="1:14" ht="39.6" customHeight="1">
       <c r="A4" s="3" t="s">
         <v>86</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>535</v>
-      </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" spans="1:14" ht="39.6" customHeight="1">
+      <c r="A5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="L4" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="M4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N4" s="3"/>
-    </row>
-    <row r="5" spans="1:14" ht="288.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="J5" s="3" t="s">
+      <c r="L5" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" spans="1:14" ht="39.6" customHeight="1">
+      <c r="A6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="L5" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N5" s="3"/>
-    </row>
-    <row r="6" spans="1:14" ht="51.75" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="G6" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="H6" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>513</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="J6" s="3" t="s">
+      <c r="L6" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="N6" s="3"/>
+    </row>
+    <row r="7" spans="1:14" ht="180.75" customHeight="1">
+      <c r="A7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="L6" s="4" t="s">
-        <v>474</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="N6" s="3"/>
-    </row>
-    <row r="7" spans="1:14" ht="323.25" customHeight="1">
-      <c r="A7" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="H7" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>559</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>560</v>
       </c>
       <c r="L7" s="4" t="s">
         <v>93</v>
@@ -6011,7 +5973,7 @@
   <sheetData>
     <row r="1" spans="1:14" ht="27.95" customHeight="1">
       <c r="A1" s="11" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
@@ -6029,7 +5991,7 @@
     </row>
     <row r="2" spans="1:14" ht="39.950000000000003" customHeight="1">
       <c r="A2" s="9" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B2" s="10"/>
       <c r="C2" s="10"/>
@@ -6050,19 +6012,19 @@
         <v>55</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>82</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>72</v>
@@ -6073,28 +6035,28 @@
     </row>
     <row r="4" spans="1:14" ht="75.95" customHeight="1">
       <c r="A4" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="D4" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="G4" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="H4" s="3" t="s">
         <v>569</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>570</v>
       </c>
     </row>
     <row r="5" spans="1:14" ht="75.95" customHeight="1">
@@ -6102,51 +6064,51 @@
         <v>62</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>5</v>
+        <v>570</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>567</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>571</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>568</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>63</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="6" spans="1:14" ht="75.95" customHeight="1">
       <c r="A6" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="F6" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>574</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>575</v>
       </c>
     </row>
     <row r="7" spans="1:14" ht="75.95" customHeight="1">
@@ -6154,25 +6116,25 @@
         <v>65</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>567</v>
-      </c>
-      <c r="D7" s="3" t="s">
+      <c r="G7" s="4" t="s">
+        <v>382</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>577</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>568</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>578</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>579</v>
       </c>
     </row>
   </sheetData>
